--- a/untitled folder/HSC_Physics_1st_Paper_Chapter_01_Physical_World_and_Measurement.xlsx
+++ b/untitled folder/HSC_Physics_1st_Paper_Chapter_01_Physical_World_and_Measurement.xlsx
@@ -1313,11 +1313,6 @@
           <t>একটি অত্যন্ত সান্দ্র মাধ্যমে ক্ষুদ্র গোলকের বেগ $v$ হলে সান্দ্র বল $F_1 = 6\pi \eta r v$। কিন্তু উচ্চ বেগে মাধ্যমে যে প্রতিরোধ বল কাজ করে তা $F_2 = k \rho^a r^b v^c$। মাত্রা বিশ্লেষণের মাধ্যমে $a, b, c$ নির্ণয় করো এবং দেখাও যে কেন উচ্চ বেগে গোলকের পৃষ্ঠতলের সান্দ্রতার চেয়ে তরলের সম্মুখভাগের গতিশক্তি প্রদান মুখ্য ভূমিকা পালন করে।</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>১. $[MLT^{-2}] = [ML^{-3}]^a [L]^b [LT^{-1}]^c = M^a L^{-3a+b+c} T^{-c}$
@@ -1421,11 +1416,6 @@
           <t>যদি আমাদের মহাবিশ্ব $d$-সংখ্যক স্থানিক মাত্রার (Spatial dimensions) হতো, তবে গাউসের সূত্র অনুযায়ী মহাকর্ষ বল $F \propto \frac{1}{r^{d-1}}$ হতো। মাত্রা বিশ্লেষণ এবং গতিবিদ্যার সাহায্যে প্রমাণ করো যে এই জগতে একটি আবদ্ধ বৃত্তাকার কক্ষপথের পর্যায়কাল $T$ ও ব্যাসার্ধ $r$-এর সম্পর্ক হবে $T \propto r^{d/2}$।</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>১. $d$-মাত্রিক ক্ষেত্রে মহাকর্ষ বলের রূপ: $F_g = \frac{G_d M m}{r^{d-1}}$।
@@ -1522,11 +1512,6 @@
           <t>তরল পৃষ্ঠে সৃষ্ট ক্ষুদ্র কৈশিক তরঙ্গের বেগ $v_c \propto T_s^a \rho^b \lambda^c$ এবং মহাকর্ষীয় তরঙ্গের বেগ $v_g \propto g^x \lambda^y$। মাত্রা বিশ্লেষণের সাহায্যে দেখাও যে যে তরঙ্গদৈর্ঘ্যে কৈশিক প্রভাব ও মহাকর্ষীয় প্রভাব সমমানের হয়, সেই সংকট তরঙ্গদৈর্ঘ্য $\lambda_c \propto \sqrt{\frac{T_s}{\rho g}}$।</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>১. কৈশিক বেগ: $[v_c] = [LT^{-1}] = [MT^{-2}]^a [ML^{-3}]^b [L]^c$। সমাধান করে: $a=1/2, b=-1/2, c=-1/2 \implies v_c \propto \sqrt{\frac{T_s}{\rho \lambda}}$।
@@ -1575,11 +1560,6 @@
           <t>নিউটনের মতে বায়ুতে শব্দের বেগ $v = \sqrt{P/\rho}$ এবং ল্যাপলাসের সংশোধিত সমীকরণ $v = \sqrt{\gamma P/\rho}$। মাত্রা বিশ্লেষণের সাহায্যে কি প্রমাণ করা সম্ভব যে নিউটনের সূত্রটিতে ভুল ছিল এবং $\gamma$ থাকা আবশ্যক? তোমার উত্তরের সপক্ষে যুক্তি দাও।</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>১. চাপ $[P] = [M L^{-1} T^{-2}]$, ঘনত্ব $[\rho] = [M L^{-3}]$।
@@ -1626,11 +1606,6 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>ইলেকট্রনের ভর $m_e$, মৌলিক আধান $e$, শূন্য মাধ্যমের ভেদনযোগ্যতা $\varepsilon_0$, এবং প্লাংক ধ্রুবক $\hbar$-এর সমন্বয়ে গঠিত কোন রাশিটি দৈর্ঘ্যের মাত্রা প্রকাশ করে? মাত্রা বিশ্লেষণের সাহায্যে হাইড্রোজেন পরমাণুর গ্রাউন্ড স্টেটের ব্যাসার্ধের সমীকরণ নির্ণয় করো।</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1683,11 +1658,6 @@
           <t>একটি সরল দোলকের সাহায্যে অভিকর্ষজ ত্বরণ $g = 4\pi^2 \frac{L}{T^2}$ পরিমাপে তারের কার্যকর দৈর্ঘ্য $L$ পরিমাপে $\pm 1\%$ এবং পর্যায়কাল $T$ পরিমাপে $\pm 2\%$ পরম আপেক্ষিক অনিশ্চয়তা বিদ্যমান। অবকলন পদ্ধতি (Differentials) ব্যবহার করে দেখাও যে $g$-এর সর্বোচ্চ সম্ভাব্য আপেক্ষিক ত্রুটি এবং গড় বর্গমূল (RMS/Quadrature) আপেক্ষিক ত্রুটির মধ্যে পার্থক্য কী এবং কেন RMS ত্রুটি অধিকতর বাস্তবসম্মত?</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>১. সমীকরণ: $\ln g = \ln(4\pi^2) + \ln L - 2\ln T$
@@ -1734,11 +1704,6 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>একটি গোলকের ব্যাসার্ধ পরিমাপে আপেক্ষিক ত্রুটি $\frac{\Delta r}{r} = +10\%$। সাধারণ রৈখিক অবকলন $\frac{\Delta V}{V} \approx 3\frac{\Delta r}{r}$ প্রয়োগ করলে আয়তনের ত্রুটি আসে $+30\%$। কিন্তু সঠিক টেলর ধারা সম্প্রসারণ ব্যবহার করে দেখাও যে প্রকৃত আয়তন বৃদ্ধির শতকরা ত্রুটি কত এবং কখন রৈখিক অবকলন পদ্ধতি অকার্যকর হয়?</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1788,11 +1753,6 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>দুটি রোধ $R_1 = (100 \pm 2)\,\Omega$ এবং $R_2 = (200 \pm 6)\,\Omega$ সমান্তরাল সমবায়ে যুক্ত করা হলো। তুল্য রোধ $R_p = \frac{R_1 R_2}{R_1 + R_2}$ পরিমাপে পরম ত্রুটি নির্ণয় করো। কেন সরাসরি গুণ ও ভাগের পৃথক আপেক্ষিক ত্রুটি যোগ করলে এখানে ভুল ফলাফল পাওয়া যায়?</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1846,11 +1806,6 @@
           <t>একটি স্বচ্ছ মাধ্যমের প্রতিসরাঙ্ক $\mu = \frac{1}{\sin \theta_c}$ সমীকরণ দ্বারা সংকট কোণ $\theta_c$ পরিমাপ করে নির্ণয় করা হয়। যদি $\theta_c$ পরিমাপে একটি ধ্রুব কোণীয় অনিশ্চয়তা $d\theta_c$ থাকে, তবে দেখাও যে প্রতিসরাঙ্কের আপেক্ষিক ত্রুটি $\frac{d\mu}{\mu} = -\cot \theta_c \, d\theta_c$। সংকট কোণ $90^\circ$ বা $0^\circ$-এর কাছাকাছি হলে ত্রুটির আচরণ কেমন হবে?</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>১. দেওয়া আছে: $\mu = (\sin \theta_c)^{-1}$
@@ -1899,11 +1854,6 @@
           <t>একটি নিরেট তারের ঘনত্ব $\rho = \frac{m}{\pi (d/2)^2 l} = \frac{4m}{\pi d^2 l}$। ভর $m$, ব্যাস $d$ এবং দৈর্ঘ্য $l$ পরিমাপে যন্ত্রের লঘিষ্ঠ গণনজনিত অনিশ্চয়তা যথাক্রমে $\Delta m, \Delta d, \Delta l$। কেন ব্যাস $d$ পরিমাপের যন্ত্রের সূক্ষ্মতা দৈর্ঘ্য $l$ পরিমাপের চেয়ে দ্বিগুণ গুরুত্বপূর্ণ?</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>১. লগারিদম নিয়ে অবকলন: $\ln \rho = \ln(4/\pi) + \ln m - 2\ln d - \ln l$
@@ -1950,11 +1900,6 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>একটি টিউনড এলসি বর্তনীর অনুরণন কম্পাঙ্ক $f_0 = \frac{1}{2\pi \sqrt{LC}}$। যদি কোনো নিয়মতান্ত্রিক কারণে ইন্ডাকট্যান্স $L$ পরিমাপে $+2\%$ ধনাত্মক ত্রুটি এবং ক্যাপাসিট্যান্স $C$ পরিমাপে $-2\%$ ঋণাত্মক ত্রুটি ঘটে, তবে অনুরণন কম্পাঙ্ক $f_0$-তে মোট নেট আপেক্ষিক ত্রুটি কত হবে?</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2006,11 +1951,6 @@
           <t>মিটার ব্রিজে অজানা রোধ $X = R \frac{l}{100 - l}$ সমীকরণে পরিমাপের সময় তারের দুই প্রান্তের ধাতব পাতের রোধের কারণে প্রান্তীয় ত্রুটি (End resistance errors) $\alpha$ এবং $\beta$ দেখা দেয়। দেখাও যে ভারসাম্য বিন্দু তারের মধ্যবিন্দু ($l \approx 50\text{ cm}$)-এর কাছাকাছি হলে কেন শতকরা ত্রুটি সর্বনিম্ন হয়?</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>১. অবকলন নিলে: $\ln X = \ln R + \ln l - \ln(100 - l)$
@@ -2060,11 +2000,6 @@
           <t>একটি ক্যালরিমিটার পরীক্ষায় প্রাথমিক তাপমাত্রা $T_1 = (20.0 \pm 0.2)^\circ\text{C}$ এবং চূড়ান্ত তাপমাত্রা $T_2 = (22.0 \pm 0.2)^\circ\text{C}$ মাপা হলো। তাপমাত্রা বৃদ্ধি $\Delta T = T_2 - T_1$-এর আপেক্ষিক শতকরা ত্রুটি কত? বিয়োগফলের ক্ষেত্রে কেন আপেক্ষিক ত্রুটি মারাত্মকভাবে বৃদ্ধি পায় (Catastrophic Cancellation)?</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>১. তাপমাত্রা বৃদ্ধি: $\Delta T = 22.0 - 20.0 = 2.0^\circ\text{C}$
@@ -2113,11 +2048,6 @@
           <t>একটি গতিশীল কণার ভরবেগ পরিমাপে অনিশ্চয়তা $+3\%$ হলে তার গতিশক্তি $E_k = \frac{p^2}{2m}$-এর শতকরা পরিবর্তন কত হবে? যদি ভরবেগের বৃদ্ধি $+100\%$ হয়, তবে সাধারণ ব্যবকলনীয় অনুমান $\Delta E_k / E_k = 2 \Delta p / p$ কেন চরম ভুল ফলাফল দেয়?</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>১. অবকলন পদ্ধতি: $E_k \propto p^2 \implies \frac{dE_k}{E_k} = 2\frac{dp}{p} = 2(+3\%) = +6\%$।
@@ -2164,11 +2094,6 @@
       <c r="G21" t="inlineStr">
         <is>
           <t>পিতলের তৈরি একটি ভার্নিয়ার ক্যালিপার্স $0^\circ\text{C}$ তাপমাত্রায় ক্যালিব্রেট করা হয়েছে। $30^\circ\text{C}$ তাপমাত্রায় এটি দিয়ে একটি স্টিলের দণ্ডের দৈর্ঘ্য মাপা হলো $L_{\text{obs}}$। পিতল ও স্টিলের রৈখিক প্রসারণ সহগ যথাক্রমে $\alpha_b$ এবং $\alpha_s$ হলে, দণ্ডটির প্রকৃত দৈর্ঘ্য $0^\circ\text{C}$-এ কত ছিল? যন্ত্রের স্কেল ও বস্তুর প্রসারণের পারস্পরিক সম্পর্ক ব্যাখ্যা করো।</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2220,11 +2145,6 @@
           <t>একটি বিশেষ ধরণের পশ্চাৎমুখী ভার্নিয়ার স্কেলে (Retrograde Vernier) ভার্নিয়ারের $n$-সংখ্যক ঘর প্রধান স্কেলের $(n+1)$-সংখ্যক ক্ষুদ্রতম ঘরের সমান। যদি প্রধান স্কেলের ১ ঘরের মান $s$ হয়, তবে ভার্নিয়ার ধ্রুবক (VC) কত হবে এবং সাধারণ ডাইরেক্ট ভার্নিয়ারের সাথে এর পাঠ গ্রহণের কৌশলের মৌলিক পার্থক্য কী?</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>১. শর্তমতে, $n \cdot v = (n+1) s \implies v = \frac{n+1}{n} s = s + \frac{s}{n}$
@@ -2274,11 +2194,6 @@
           <t>একটি স্ক্রু গজের সাহায্যে খুব সূক্ষ্ম তারের ব্যাস মাপার সময় র্যাচেটের কটকট শব্দ হওয়া পর্যন্ত না ঘুরিয়ে যদি অনভিজ্ঞ কোনো শিক্ষার্থী স্পিন্ডলকে হাত দিয়ে অতিরিক্ত জোরে ঘোরায়, তবে পাঠে কী ধরনের নিয়মতান্ত্রিক ত্রুটি দেখা দেবে? পদার্থের স্থিতিস্থাপক ধর্মের আলোকে এই ত্রুটির উৎস ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>১. র্যাচেট মেকানিজম একটি নির্দিষ্ট সমমানের টর্ক বা চাপ (Constant clamping force) নিশ্চিত করে।
@@ -2328,11 +2243,6 @@
           <t>স্ক্রু গজ বা ট্রাভেলিং মাইক্রোস্কোপে 'পিছট ত্রুটি' (Backlash Error) কেন তৈরি হয়? এই ত্রুটি পরিহারের জন্য পরিমাপকালে স্ক্রুটিকে সর্বদা একই দিকে ঘোরানোর নির্দেশ দেওয়া হয় কেন?</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>১. দীর্ঘকাল ব্যবহারের ফলে নাট এবং স্ক্রুর প্যাঁচের মধ্যবর্তী অংশের ধাতু ক্ষয়প্রাপ্ত হয়ে ক্ষুদ্র ফাঁকা স্থান (Play or clearance) সৃষ্টি হয়।
@@ -2378,11 +2288,6 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>একটি স্ফেরোমিটারের তিনটি পায়ের গড় দূরত্ব $a$ এবং মধ্যবর্তী স্ক্রুর উচ্চতা $h$ হলে গোলীয় তলের বক্রতার ব্যাসার্ধ $R = \frac{a^2}{6h} + \frac{h}{2}$। যদি সমবাহু ত্রিভুজের তিনটি পায়ের একটি পা সামান্য বেঁকে গিয়ে দূরত্বগুলোর একটি $a_1 \neq a_2$ হয়, তবে জ্যামিতিক উপপাদ্য ব্যবহার করে দেখাও যে কীভাবে সংশোধিত ব্যাসার্ধ হিসাব করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2542,11 +2447,6 @@
           <t>একটি ডিজিটাল ভার্নিয়ার ক্যালিপার্স ডিসপ্লেতে পাঠ $12.34\text{ mm}$ প্রদর্শন করে। কিন্তু একটি এনালগ ভার্নিয়ার ক্যালিপার্সে শিক্ষার্থী খালি চোখে দাগ সমাপতন দেখে। পরিমাপ বিজ্ঞানের (Metrology) দৃষ্টিতে ডিজিটাল মিটারের অন্তর্নিহিত কোয়ান্টাইজেশন অনিশ্চয়তা (Quantization uncertainty) $\pm 0.5\text{ LSB}$ কেন বিদ্যমান থাকে?</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>১. ডিজিটাল সিস্টেমে এনালগ অবস্থান সেন্সর (ক্যাপাসিটিভ বা অপটিক্যাল এনকোডার) সংকেতকে ডিসক্রিট বাইনারি মানে রূপান্তর করে।
@@ -2594,11 +2494,6 @@
           <t>এনালগ ভার্নিয়ার ক্যালিপার্সে মূল স্কেল এবং ভার্নিয়ার স্কেলের মধ্যবর্তী ফাঁকা স্থান (Bevel gap)-এর জন্য লম্বন ত্রুটি (Parallax Error) কীভাবে সৃষ্টি হয়? আধুনিক ত্রুটিমুক্ত ভার্নিয়ারে বেভেলড এজ (Beveled edge) কেন ব্যবহার করা হয়?</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>১. যদি প্রধান স্কেল ও ভার্নিয়ার স্কেল দুটি ভিন্ন উচ্চতার সমতলে থাকে, তবে তীর্যকভাবে তাকালে প্রতিসরণ বা জ্যামিতিক দৃষ্টিরেখার স্থানচ্যুতির কারণে ভার্নিয়ারের ভুল দাগকে মূল স্কেলের সাথে সমপাতিত মনে হয়।
@@ -2643,11 +2538,6 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>একটি ফাঁপা পাইপের অভ্যন্তরীণ ব্যাস মাপার জন্য ভার্নিয়ার ক্যালিপার্সের ওপরের অন্তঃপরিমাপক চোয়াল (Upper jaws) ব্যবহার করা হলো। যদি চোয়ালগুলোর প্রান্ত ক্ষয়প্রাপ্ত হয়ে তীক্ষ্ণতা হারিয়ে সামান্য চ্যাপ্টা হয়ে যায়, তবে পরিমাপকৃত পাঠে কী ধরনের ত্রুটি আসবে?</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2695,11 +2585,6 @@
       <c r="G31" t="inlineStr">
         <is>
           <t>একটি স্ফেরোমিটার দিয়ে উত্তল দর্পণের বক্রতার ব্যাসার্ধ মাপার সময় কেন্দ্রীয় স্ক্রুটি যদি উত্তল তলে সামান্য চাপ দেয়, তবে পাঠের ওপর কী প্রভাব পড়বে? ফোকাস দূরত্ব $f = R/2$ হওয়ায় এই ত্রুটি কীভাবে ফোকাস দূরত্বে দ্বিগুণ অনুপাতিক হয়ে বিস্তার লাভ করে?</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2750,11 +2635,6 @@
           <t>একটি পরীক্ষায় চারজন শিক্ষার্থী অভিকর্ষজ ত্বরণ $g$-এর পাঠ নিল: শিক্ষার্থী ক: $9.81, 9.80, 9.82\text{ m/s}^2$; শিক্ষার্থী খ: $9.5512, 9.5511, 9.5513\text{ m/s}^2$। কোন শিক্ষার্থীর পরিমাপ অধিক যথার্থ (Accurate) এবং কার পরিমাপ অধিক সূক্ষ্ম (Precise)? ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>১. যথার্থতা (Accuracy) নির্দেশ করে পরিমাপকৃত গড় মান তাত্ত্বিক বা আদর্শ মানের ($9.81\text{ m/s}^2$) কতটা কাছাকাছি। শিক্ষার্থী ক-এর গড় $9.81\text{ m/s}^2$ আদর্শ মানের সমান।
@@ -2799,11 +2679,6 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>$0.0050200\text{ m}$ সংখ্যাটিতে কয়টি তাৎপর্যপূর্ণ অঙ্ক (Significant figures) বিদ্যমান? প্রথম তিনটি শূন্য এবং শেষের দুটি শূন্যের তাৎপর্যগত পার্থক্য বৈজ্ঞানিক স্বরলিপির (Scientific notation) সাহায্যে প্রমাণ করো।</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2852,11 +2727,6 @@
       <c r="G34" t="inlineStr">
         <is>
           <t>তিনটি ভর যথাক্রমে $2.1\text{ kg}$, $12.345\text{ g}$, এবং $0.0005\text{ kg}$। এই তিনটি ভরের সঠিক মোট যোগফল তাৎপর্যপূর্ণ অঙ্কের সঠিক নিয়মে কত কিলোগ্রাম হবে?</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2910,11 +2780,6 @@
           <t>রসায়নে বা পদার্থবিজ্ঞানে $x = 4.56 \times 10^{-5}$ হলে $\log_{10}(x)$ নির্ণয় করো। লগারিদমের ক্ষেত্রে বৈশিষ্ট্য (Characteristic) এবং ম্যান্টিসা (Mantissa)-র তাৎপর্যপূর্ণ অঙ্কের আন্তর্জাতিক নিয়ম ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>১. $\log_{10}(4.56 \times 10^{-5}) = \log_{10}(4.56) + \log_{10}(10^{-5}) = 0.658965 - 5 = -4.341035$
@@ -2960,11 +2825,6 @@
       <c r="G36" t="inlineStr">
         <is>
           <t>একটি কোণ মাপা হলো $\theta = 45.0^\circ$। $\tan \theta$-এর মান কত এবং এই পরিমাপে আপেক্ষিক ত্রুটি $d\theta = 0.1^\circ$ হলে $\tan \theta$-র মানের বিস্তার কত হবে?</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3016,11 +2876,6 @@
           <t>রাউন্ডিং অফের আধুনিক মেট্রোলজিকাল নীতিতে 'Round to nearest even' বা যুগ্মকরণ নিয়ম কেন ব্যবহার করা হয়? উদাহরণ হিসেবে $4.35$ এবং $4.45$-কে দশমিকের পর এক ঘর পর্যন্ত রাউন্ড অফ করে দেখাও।</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>১. যদি কোনো সংখ্যা ঠিক মাঝামাঝি $5$-এ শেষ হয়, তবে চিরায়ত নিয়মে সর্বদা উপরে তুলে দিলে (Round up) যোগ বা গড়ে নিয়মতান্ত্রিক ধনাত্মক পক্ষপাত তৈরি হয়।
@@ -3066,11 +2921,6 @@
       <c r="G38" t="inlineStr">
         <is>
           <t>একটি ১২-বিট ডিজিটাল ভোল্টমিটার $0$ থেকে $10.0\text{ V}$ পর্যন্ত ভোল্টেজ মাপতে পারে। এই ভোল্টমিটারের ১টি LSB (Least Significant Bit)-এর মান কত? এর দ্বারা পরিমাপকৃত ভোল্টেজের অন্তর্নিহিত পরম কোয়ান্টাইজেশন অনিশ্চয়তা কত?</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3121,11 +2971,6 @@
           <t>একটি ঘনকের আয়তন $V = 9.0\text{ cm}^3$। এর বাহুর দৈর্ঘ্য $a = V^{1/3}$ তাৎপর্যপূর্ণ অঙ্কের সঠিক নিয়মে কত হবে? ক্যালকুলেটর ডিসপ্লেতে প্রদর্শিত $2.08008...$-এর কয়টি অঙ্ক গ্রহণযোগ্য?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>১. প্রদত্ত আয়তনে তাৎপর্যপূর্ণ অঙ্ক সংখ্যা ২ ($9.0$)।
@@ -3173,11 +3018,6 @@
           <t>একটি তারের ব্যাসের ১০ বার স্বাধীন পরিমাপ নেওয়া হলো। গড় মান $\ar{d}$ এবং স্ট্যান্ডার্ড ডেভিয়েশন $\sigma$ পাওয়া গেল। মেট্রোলজিতে $68.3\%$, $95.4\%$ এবং $99.7\%$ আত্মবিশ্বাস সীমা (Confidence interval) বলতে কী বোঝায়? একক পরিমাপের বিচ্যুতির সাথে গড়ের প্রমাণ বিচ্যুতির (Standard error of the mean) সম্পর্ক কী?</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>১. গাউসিয়ান বন্টনে দৈব ত্রুটিযুক্ত পাঠের $68.3\%$ মান $[\bar{d}-\sigma, \ar{d}+\sigma]$ ব্যবধিতে থাকে, $95.4\%$ থাকে $2\sigma$ তে এবং $99.7\%$ থাকে $3\sigma$ তে।
@@ -3225,11 +3065,6 @@
           <t>যদি একটি স্কেলের ক্ষুদ্রতম দাগ $1\text{ mm}$ হয়, তবে কোনো কাঠিটির প্রান্ত $2.4\text{ cm}$ এবং $2.5\text{ cm}$-এর মাঝামাঝি থাকলে শিক্ষার্থী $2.45\text{ cm}$ লিখতে পারে কি না? মেট্রোলজির দৃষ্টিতে অনুমিত অঙ্ক (Estimated digit)-এর নিয়ম ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>১. মেট্রোলজির আন্তর্জাতিক রীতি অনুসারে, একটি অ্যানালগ স্কেলের ক্ষুদ্রতম ঘরের ভগ্নাংশ (সাধারণত অর্ধ-ঘর বা এক-পঞ্চমাংশ) চোখ দিয়ে অনুমান করে পাঠ নেওয়া হয়।
@@ -3277,11 +3112,6 @@
           <t>প্রকৃতির চারটি মৌলিক বলের মধ্যে মহাকর্ষ বল সবচেয়ে দুর্বল হওয়া সত্ত্বেও এটিই কেন মহাজাগতিক স্কেলে নক্ষত্র, গ্রহ ও ছায়াপথকে শাসন করে? অন্যদিকে সবল নিউক্লীয় বল তীব্রতম ($10^{38}$ গুণ শক্তিশালী) হওয়া সত্ত্বেও দৈনন্দিন জীবনে আমরা এটি অনুভব করি না কেন?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>১. তড়িৎ-চৌম্বক বল মহাকর্ষের চেয়ে কোটি কোটি গুণ শক্তিশালী হলেও মহাবিশ্বে ধনাত্মক ও ঋণাত্মক আধান প্রায় সমপরিমাণে থাকায় বৃহৎ স্কেলে তারা পরস্পরকে নিষ্ক্রিয় করে দেয়। কিন্তু ভর সর্বদা ধনাত্মক হওয়ায় মহাকর্ষের প্রভাব কেবল যোগ হয় এবং অসীম দূরত্বে কার্যকর থাকে।
@@ -3326,11 +3156,6 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>হাইজেনবার্গের শক্তি-সময় অনিশ্চয়তা নীতি $\Delta E \cdot \Delta t \sim \hbar$ ব্যবহার করে দেখাও যে একটি মধ্যস্থতাকারী কণার (Exchange particle) ভর $m$ হলে সেই বলের পাল্লা $R \approx \frac{\hbar}{m c}$। ফোটন ও মহাকর্ষীয় কণার পাল্লা কেন অসীম?</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3382,11 +3207,6 @@
           <t>আবদুস সালাম, শেলডন গ্ল্যাশো এবং স্টিভেন ওয়েইনবার্গ কর্তৃক প্রদত্ত 'ইলেক্ট্রোউইক একীকরণ' (Electroweak Unification) তত্ত্বে কোন দুটি মৌলিক বলকে একীভূত করা হয় এবং কত শক্তি বা তাপমাত্রা স্কেলে এদের আচরণ অভিন্ন হয়ে ওঠে?</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>১. সাধারণ নিম্ন শক্তিতে দুর্বল বল (যা $\beta$-ক্ষয়ের জন্য দায়ী) এবং তড়িৎ-চৌম্বক বল সম্পূর্ণ ভিন্ন আচরণ করে; কারণ দুর্বল বলের বাহক $W^\pm, Z^0$ বোসন কণাগুলো অত্যন্ত ভারী ($\approx 80-91\text{ GeV/c}^2$), কিন্তু ফোটন ভরহীন।
@@ -3431,11 +3251,6 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>১৯৫৬ সালে চিয়েন-শিউং উ (Chien-Shiung Wu) কোবাল্ট-৬০ নিউক্লিয়াসের $\beta$-ক্ষয় পরীক্ষার মাধ্যমে প্রমাণ করেন যে প্রকৃতিতে দুর্বল বল প্যারিটি প্রতিসাম্য (Parity Symmetry) বা দর্পণ প্রতিসাম্য ভঙ্গ করে। পরিমাপের ক্ষেত্রে প্যারিটি লঙ্ঘনের ভৌত তাৎপর্য কী?</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3532,11 +3347,6 @@
           <t>যদি অতিরিক্ত ক্ষুদ্র গুটানো স্থানিক মাত্রা (Extra Compactified Dimensions - ADD মডেল) বিদ্যমান থাকে, তবে অত্যন্ত ক্ষুদ্র দূরত্বে ($r &lt; R_{\text{extra}}$) মহাকর্ষ বলের রূপ পরিবর্তিত হয়ে $F \propto \frac{1}{r^{2+n}}$ হতে পারে। অত্যাধুনিক টরশন ব্যালেন্স দিয়ে উপ-মিলিমিটার স্কেলে মহাকর্ষ পরিমাপের চ্যালেঞ্জগুলো কী কী?</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>১. নিউটনের মহাকর্ষীয় ধ্রুবক $G$ অত্যন্ত দুর্বল হওয়ায় ক্ষুদ্র ভরের মধ্যে মহাকর্ষ বল $10^{-12}\text{ N}$-এর নিচে নেমে যায়।
@@ -3584,11 +3394,6 @@
           <t>আধুনিক কোয়ান্টাম ফিল্ড থিওরিতে বলকে কোনো 'দূরবর্তী ক্রিয়া' (Action at a distance) হিসেবে না দেখে ভার্চুয়াল কণার আদান-প্রদান হিসেবে ব্যাখ্যা করা হয় কেন? ভরবেগ সংরক্ষণের সাথে এর সম্পর্ক ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>১. নিউটনের ধারণায় একটি ভর সরালে মুহূর্তের মধ্যে অপর ভর তা অনুভব করে, যা তথ্যের আলোর চেয়ে দ্রুত পরিবহণ নিষিদ্ধকারী আপেক্ষিকতার পরিপন্থী।
@@ -3633,11 +3438,6 @@
       <c r="G49" t="inlineStr">
         <is>
           <t>গ্র্যান্ড ইউনিফাইড থিওরি (GUT)-তে সবল, দুর্বল ও তড়িৎ-চৌম্বক বলকে প্রায় $10^{16}\text{ GeV}$ শক্তিতে একীভূত করা হয়। এই তত্ত্বে প্রোটন কেন চিরস্থায়ী কণা নয়? সুপার-কামিওকান্দে ডিটেক্টরে প্রোটনের আয়ুষ্কাল পরিমাপের মেট্রোলজিকাল গুরুত্ব কী?</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3687,11 +3487,6 @@
           <t>সবল নিউক্লীয় বলের ক্ষেত্রে ফ্রাঙ্ক উইলচেক, ডেভিড গ্রস এবং ডেভিড পলিটজার আবিষ্কৃত 'অ্যাসিম্পটোটিক ফ্রিডম' কী? কোয়ার্কগুলোর মধ্যবর্তী দূরত্ব অত্যন্ত কমে গেলে বলের তীব্রতা হ্রাস পায় কেন?</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>১. সাধারণ তড়িৎ-চৌম্বক বলে আধানের কাছে গেলে বল বাড়ে। কিন্তু সবল বলে গ্লুয়নগুলো নিজেরাও কালার আধান বহন করায় 'অ্যান্টি-স্ক্রিনিং' প্রভাব সৃষ্টি করে।
@@ -3737,11 +3532,6 @@
       <c r="G51" t="inlineStr">
         <is>
           <t>তাত্ত্বিক পদার্থবিজ্ঞানের 'হায়ারার্কি সমস্যা' (Hierarchy Problem) কী? দুটি প্রোটনের মধ্যকার মহাকর্ষ বল ও কুলম্ব বলের অনুপাত নির্ণয় করে এর তীব্র অসঙ্গতি দেখাও।</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3776,7 +3566,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ভার্নিয়ার ধ্রুবক ও ঋণাত্মক যান্ত্রিক ত্রুটি</t>
+          <t>স্লাইড ক্যালিপার্স ও ভার্নিয়ার ধ্রুবক</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3785,12 +3575,12 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>##GEO:vernier[size:medium]##
-একটি স্লাইড ক্যালিপার্সের প্রধান স্কেলের ক্ষুদ্রতম ১ ঘরের মান $1\text{{ mm}}$ এবং প্রধান স্কেলের $19$ ঘর ভার্নিয়ার স্কেলের $20$ ঘরের সমান। চোয়াল দুটি পরস্পর স্পর্শ করা অবস্থায় ভার্নিয়ারের শূন্য দাগ প্রধান স্কেলের শূন্য দাগের বাঁয়ে থাকে এবং ভার্নিয়ারের $4$ নং দাগ প্রধান স্কেলের একটি দাগের সাথে হুবহু মিলে যায়। একটি নিরেট তামার গোলকের ব্যাস পরিমাপের সময় প্রধান স্কেল পাঠ $3.2\text{{ cm}}$ এবং ভার্নিয়ার সমপাতন $14$ পাওয়া গেল। গোলকটির প্রকৃত আয়তন কত?</t>
+একটি গোলকের ব্যাস নির্ণয়ে স্লাইড ক্যালিপার্সে মূল স্কেল পাঠ $4.3\text{ cm}$, ভার্নিয়ার সমপাতন $7$ পাওয়া গেল। মূল স্কেলের $1\text{ mm}$ ক্ষুদ্রতম ঘর এবং ভার্নিয়ারের $10$ ঘর মূল স্কেলের $9$ ঘরের সমান। কোনো যান্ত্রিক ত্রুটি না থাকলে গোলকটির সঠিক ব্যাস ও আয়তন নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3800,24 +3590,14 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ভার্নিয়ার ধ্রুবক, $VC = 1 - \frac{19}{20} = 0.05\text{{ mm}} = 0.005\text{{ cm}}$।
-যেহেতু ভার্নিয়ারের শূন্য দাগ প্রধান স্কেলের শূন্যের বাঁয়ে থাকে, যান্ত্রিক ত্রুটি ঋণাত্মক:
-$e = -(20 - 4) \times VC = -16 \times 0.005\text{{ cm}} = -0.08\text{{ cm}}$ (অথবা সমপাতন ৪ হলে ঋণাত্মক ত্রুটি $e = -4 \times 0.005 = -0.02\text{{ cm}}$)। প্রচলিত নিয়মে $e = -4 \times 0.005 = -0.02\text{{ cm}}$।
-পরিমাপিত পাঠ $L' = M + (V \times VC) = 3.2 + (14 \times 0.005) = 3.27\text{{ cm}}$।
-প্রকৃত ব্যাস $d = L' - e = 3.27 - (-0.02) = 3.29\text{{ cm}}$।
-ব্যাসার্ধ $r = 1.645\text{{ cm}}$।
-$\therefore$ আয়তন $V = \frac{4}{3}\pi r^3 = \frac{4}{3}\pi (1.645)^3 \approx 18.42\text{{ cm}}^3$।</t>
+          <t>ভার্নিয়ার ধ্রুবক $VC = 1 - \frac{9}{10} = 0.1\text{ mm} = 0.01\text{ cm}$। পাঠ $D = M + V \times VC = 4.3 + 7 \times 0.01 = 4.37\text{ cm}$। ব্যাসার্ধ $R = 2.185\text{ cm}$। আয়তন $V = \frac{4}{3}\pi R^3 = \frac{4}{3}\pi (2.185)^3 = 43.68\text{ cm}^3$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>$18.42\text{{ cm}}^3$</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>ব্যাস $D = 4.37\text{ cm}$, আয়তন $V = 43.68\text{ cm}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3837,7 +3617,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ফাঁপা নলের পুরুত্ব ও ঘনত্ব নির্ণয়</t>
+          <t>স্লাইড ক্যালিপার্স ও ভার্নিয়ার ধ্রুবক</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3850,32 +3630,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=4,h=8][size:medium]##
-$VC = 0.002\text{{ cm}}$ বিশিষ্ট ট্রাভেলিং মাইক্রোস্কোপ দিয়ে একটি ফাঁপা কাচ নলের বহির্ব্যাস ও অন্তর্ব্যাস পরিমাপে প্রধান স্কেল ও ভার্নিয়ার পাঠ পাওয়া গেল যথাক্রমে বহির্ব্যাসের ক্ষেত্রে $M_1 = 2.45\text{{ cm}}, V_1 = 12$ এবং অন্তর্ব্যাসের ক্ষেত্রে $M_2 = 1.85\text{{ cm}}, V_2 = 8$। নলটির দৈর্ঘ্য $l = 10.0\text{{ cm}}$ এবং ভর $m = 48.2\text{ g}$ হলে কাচের ঘনত্ব কত?</t>
+          <t>##GEO:vernier[size:medium]##
+একটি স্লাইড ক্যালিপার্সে প্রধান স্কেলের ক্ষুদ্রতম ভাগ $1\text{ mm}$ এবং ভার্নিয়ার স্কেলের $20$ ভাগ প্রধান স্কেলের $19$ ভাগের সমান। চোয়াল দুটি বন্ধ থাকা অবস্থায় ভার্নিয়ারের শূন্য দাগ প্রধান স্কেলের শূন্যের ডানে $0.02\text{ cm}$ দূরে থাকে (ধনাত্মক যান্ত্রিক ত্রুটি)। একটি দণ্ডের দৈর্ঘ্য মাপার সময় মূল স্কেল পাঠ $5.6\text{ cm}$ এবং ভার্নিয়ার সমপাতন $12$ পাওয়া গেলে দণ্ডটির প্রকৃত দৈর্ঘ্য কত?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=4,h=8][size:medium]##</t>
+          <t>##GEO:vernier[size:medium]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>বহির্ব্যাস $D_o = 2.45 + (12 \times 0.002) = 2.474\text{{ cm}} \implies R_o = 1.237\text{{ cm}}$।
-অন্তর্ব্যাস $D_i = 1.85 + (8 \times 0.002) = 1.866\text{{ cm}} \implies R_i = 0.933\text{{ cm}}$।
-কাচের কার্যকর আয়তন $V = \pi (R_o^2 - R_i^2) l = \pi (1.237^2 - 0.933^2) \times 10.0 = \pi (1.530 - 0.870) \times 10 = 20.42\text{{ cm}}^3$।
-ঘনত্ব $\rho = \frac{m}{V} = \frac{48.2}{20.42} \approx 2.36\text{ g/cm}^3$।</t>
+          <t>ভার্নিয়ার ধ্রুবক $VC = \frac{1\text{ mm}}{20} = 0.05\text{ mm} = 0.005\text{ cm}$। দৃশ্যমান পাঠ $= 5.6 + 12 \times 0.005 = 5.66\text{ cm}$। ধনাত্মক ত্রুটি $+0.02\text{ cm}$ বিয়োগ করে প্রকৃত পাঠ $= 5.66 - 0.02 = 5.64\text{ cm}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>$2.36\text{ g/cm}^3$</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>প্রকৃত দৈর্ঘ্য $L = 5.64\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3895,47 +3668,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>স্ক্রু গজের পিচ ও পজিটিভ ব্যাকল্যাশ ত্রুটি</t>
+          <t>স্লাইড ক্যালিপার্স ও ভার্নিয়ার ধ্রুবক</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:medium]##
-একটি স্ক্রু গজে বৃত্তাকার স্কেলকে ৪ বার পূর্ণ ঘূর্ণন দিলে রৈখিক স্কেলে $2\text{{ mm}}$ সরণ ঘটে। বৃত্তাকার স্কেলের মোট ভাগসংখ্যা ৫০। স্ক্রুটির সমতল প্রান্তদ্বয় যুক্ত করলে বৃত্তাকার স্কেলের ৩নং দাগ রৈখিক স্কেলের রেফারেন্স রেখার নিচে থাকে। এর সাহায্যে একটি সূক্ষ্ম টাংস্টেন তারের ব্যাস পরিমাপে রৈখিক পাঠ $1.5\text{{ mm}}$ এবং বৃত্তাকার পাঠ ৩৭ পাওয়া গেলে তারটির প্রস্থচ্ছেদের ক্ষেত্রফল কত?</t>
+          <t>##GEO:vernier[size:medium]##
+উন্নত গবেষণাগারের একটি বিশেষ ভার্নিয়ার ক্যালিপার্সে প্রধান স্কেলের প্রতি ভাগের মান $0.5\text{ mm}$ এবং ভার্নিয়ারের $50$ ভাগ প্রধান স্কেলের $49$ ভাগের সমতুল্য। চোয়াল বদ্ধ অবস্থায় ভার্নিয়ারের শূন্য রেখা মূল স্কেলের শূন্যের বামে থাকে এবং ঋণাত্মক ত্রুটির মান $-0.015\text{ cm}$। একটি ধাতব ঘনকের বাহু পরিমাপে মূল পাঠ $3.25\text{ cm}$ এবং সমপাতন $34$ হলে ঘনকের আয়তন কত?</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:medium]##</t>
+          <t>##GEO:vernier[size:medium]##</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>পিচ $= \frac{2\text{{ mm}}}{4} = 0.5\text{{ mm}}$।
-লঘিষ্ঠ গণন $LC = \frac{0.5}{50} = 0.01\text{{ mm}}$।
-শূন্য ত্রুটি (ধনাত্মক) $e = +3 \times 0.01 = +0.03\text{{ mm}}$।
-আপাত পাঠ $= 1.5 + (37 \times 0.01) = 1.87\text{{ mm}}$।
-প্রকৃত ব্যাস $d = 1.87 - 0.03 = 1.84\text{{ mm}} \implies r = 0.92\text{{ mm}}$।
-ক্ষেত্রফল $A = \pi r^2 = \pi (0.92)^2 \approx 2.66\text{{ mm}}^2$।</t>
+          <t>$VC = \frac{0.5\text{ mm}}{50} = 0.01\text{ mm} = 0.001\text{ cm}$। পর্যবেক্ষণকৃত পাঠ $= 3.25 + 34 \times 0.001 = 3.284\text{ cm}$। প্রকৃত পাঠ $= 3.284 - (-0.015) = 3.299\text{ cm}$। আয়তন $V = a^3 = (3.299)^3 \approx 35.80\text{ cm}^3$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>$2.66\text{{ mm}}^2$</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>আয়তন $V = 35.80\text{ cm}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3955,7 +3719,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>স্ফেরোমিটার ও বক্রতার ব্যাসার্ধ</t>
+          <t>স্লাইড ক্যালিপার্স ও ভার্নিয়ার ধ্রুবক</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3968,32 +3732,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>##GEO:sphere[r=5][size:medium]##
-একটি স্ফেরোমিটারের তিনটি সমবাহু পায়ের গড় দূরত্ব $a = 4.5\text{{ cm}}$। সমতল কাচ পাতের ওপর পাঠ নেওয়ার পর একটি উত্তল লেন্সের গোলীয় তলে রেখে কেন্দ্রীয় স্ক্রুকে ঘোরাতে গিয়ে দেখা গেল রৈখিক স্কেল পাঠ $h_0 = 1\text{{ mm}}$ এবং বৃত্তাকার স্কেলের মোট ১০০ ভাগের মধ্যে ৪২ ভাগ ঘুরেছে (পিচ $0.5\text{{ mm}}$)। উত্তল তলটির বক্রতার ব্যাসার্ধ $R$ কত?</t>
+          <t>##GEO:vernier[size:medium]##
+একটি ত্রুটিপূর্ণ ক্যালিপার্সে প্রধান স্কেলের প্রতি ঘর $1\text{ mm}$ এবং ভার্নিয়ারের $20$ ভাগ প্রধান স্কেলের $18$ ভাগের সমান। একটি পাইপের বহিঃব্যাস মাপতে গিয়ে মূল পাঠ $7.8\text{ cm}$ এবং ভার্নিয়ার পাঠ $14$ হলে পাইপের বাইরের ব্যাস কত?</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>##GEO:sphere[r=5][size:medium]##</t>
+          <t>##GEO:vernier[size:medium]##</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>$LC = \frac{0.5}{100} = 0.005\text{{ mm}}$।
-উত্তল তলের উচ্চতা $h = 1\text{{ mm}} + (42 \times 0.005\text{{ mm}}) = 1.21\text{{ mm}} = 0.121\text{{ cm}}$।
-বক্রতার ব্যাসার্ধের সূত্র: $R = \frac{a^2}{6h} + \frac{h}{2}$।
-$R = \frac{(4.5)^2}{6 \times 0.121} + \frac{0.121}{2} = \frac{20.25}{0.726} + 0.0605 = 27.89 + 0.06 = 27.95\text{{ cm}}$।</t>
+          <t>ভার্নিয়ার ধ্রুবক $VC = 1\text{ mm} - \frac{18}{20}\text{ mm} = 0.1\text{ mm} = 0.01\text{ cm}$। পাঠ $D = 7.8 + 14 \times 0.01 = 7.94\text{ cm}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>$28.27\text{{ cm}}$</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>বহিঃব্যাস $D = 7.94\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4013,7 +3770,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>পরিমাপের শতকরা ত্রুটির সঞ্চারণ (Error Propagation)</t>
+          <t>স্লাইড ক্যালিপার্স ও ভার্নিয়ার ধ্রুবক</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4022,35 +3779,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>##GEO:cube[s=5][size:small]##
-একটি ঘনকের ভর পরিমাপে ত্রুটি $\pm 1.5\%$ এবং এক ধারের দৈর্ঘ্য পরিমাপে ত্রুটি $\pm 2.0\%$ হলে, উক্ত ঘনকের উপাদানের ঘনত্ব নির্ণয়ে সর্বোচ্চ সম্ভাব্য শতকরা ত্রুটি কত হবে?</t>
+          <t>##GEO:circle[r=3][size:small]##
+একটি ফাঁপা গোলকের অন্তঃব্যাস ও বহিঃব্যাস মাপতে স্লাইড ক্যালিপার্সে যথাক্রমে $2.14\text{ cm}$ ও $2.86\text{ cm}$ পাঠ পাওয়া গেল ($VC = 0.01\text{ cm}$)। গোলকটির উপাদানের আয়তন নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>##GEO:cube[s=5][size:small]##</t>
+          <t>##GEO:circle[r=3][size:small]##</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ঘনত্ব $\rho = \frac{m}{V} = \frac{m}{L^3} = m L^{-3}$।
-সর্বোচ্চ আপেক্ষিক ত্রুটি: $\frac{\Delta \rho}{\rho} = \frac{\Delta m}{m} + 3 \frac{\Delta L}{L}$।
-$\therefore \frac{\Delta \rho}{\rho} \times 100\% = 1.5\% + 3(2.0\%) = 1.5\% + 6.0\% = 7.5\%$।</t>
+          <t>বহিঃব্যাসার্ধ $R_2 = \frac{2.86}{2} = 1.43\text{ cm}$, অন্তঃব্যাসার্ধ $R_1 = \frac{2.14}{2} = 1.07\text{ cm}$। উপাদানের আয়তন $V = \frac{4}{3}\pi (R_2^3 - R_1^3) = \frac{4}{3}\pi (2.924 - 1.225) = 7.07\text{ cm}^3$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>$\pm 7.5\%$</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>উপাদানের আয়তন $V = 7.07\text{ cm}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4070,7 +3821,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>সরল দোলকের সাহায্যে $g$ নির্ণয়ে ত্রুটি বিশ্লেষণ</t>
+          <t>স্লাইড ক্যালিপার্স ও ভার্নিয়ার ধ্রুবক</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4083,33 +3834,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(15)[size:medium]##
-একটি সরল দোলকের কার্যকর দৈর্ঘ্য $L = (100.0 \pm 0.1)\text{{ cm}}$। একটি স্টপওয়াচ দিয়ে ২০টি পূর্ণ দোলনের সময় পরিমাপ করে পাওয়া গেল $t = (40.0 \pm 0.2)\text{{ s}}$। অভিকর্ষজ ত্বরণ $g$-এর মানে শতকরা কত ত্রুটি ঘটবে এবং $g$-এর চূড়ান্ত মান ত্রুটিসহ প্রকাশ কর।</t>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##
+একটি সিলিন্ডারের উচ্চতা নির্ণয়ে মূল স্কেল পাঠ $6.4\text{ cm}$, ভার্নিয়ার সমপাতন $8$ এবং যান্ত্রিক ত্রুটি $+0.03\text{ cm}$ ($VC = 0.01\text{ cm}$)। সিলিন্ডারটির সঠিক উচ্চতা কত?</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(15)[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>পর্যায়কাল $T = \frac{t}{n} \implies \frac{\Delta T}{T} = \frac{\Delta t}{t} = \frac{0.2}{40.0} = 0.005$।
-আমরা জানি, $T = 2\pi \sqrt{\frac{L}{g}} \implies g = 4\pi^2 \frac{L}{T^2}$।
-$\frac{\Delta g}{g} = \frac{\Delta L}{L} + 2\frac{\Delta T}{T} = \frac{0.1}{100.0} + 2(0.005) = 0.001 + 0.010 = 0.011 = 1.1\%$।
-$g = 4\pi^2 \frac{1.0}{(2.0)^2} = \pi^2 \approx 9.87\text{ m/s}^2$।
-$\Delta g = 9.87 \times 0.011 \approx 0.11\text{ m/s}^2$।</t>
+          <t>পর্যবেক্ষিত উচ্চতা $= 6.4 + 8 \times 0.01 = 6.48\text{ cm}$। প্রকৃত উচ্চতা $h = 6.48 - 0.03 = 6.45\text{ cm}$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>$g = (9.87 \pm 0.11)\text{ m/s}^2$ (শতকরা ত্রুটি $1.1\%$)</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>সঠিক উচ্চতা $h = 6.45\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4129,43 +3872,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>রোধ ও তড়িৎ প্রবাহ পরিমাপে ক্ষমতার ত্রুটি</t>
+          <t>স্লাইড ক্যালিপার্স ও ভার্নিয়ার ধ্রুবক</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##
-একটি রোধকের মধ্য দিয়ে বিদ্যুৎ প্রবাহিত হচ্ছে। প্রবাহ পরিমাপে সম্ভাব্য ত্রুটি $\pm 2\%$ এবং রোধের মানে ত্রুটি $\pm 1\%$। রোধকটিতে ব্যয়িত বৈদ্যুতিক ক্ষমতা $P = I^2 R$ নির্ণয়ে শতকরা কত ত্রুটি হবে?</t>
+          <t>##GEO:vernier[size:medium]##
+একটি বিশেষ ভার্নিয়ার স্কেলে প্রধান স্কেলের $0.5\text{ mm}$ ঘরকে ভার্নিয়ারের $25$ ভাগে ভাগ করা হয়েছে ($25\text{ VSD} = 24\text{ MSD}$)। পাঠ $4.15\text{ cm}$ এবং সমপাতন $17$ হলে সঠিক পরিমাপ কত?</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-resistors[size:medium]##</t>
+          <t>##GEO:vernier[size:medium]##</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>$P = I^2 R \implies \frac{\Delta P}{P} = 2\frac{\Delta I}{I} + \frac{\Delta R}{R}$।
-শতকরা ত্রুটি $= 2(2\%) + 1\% = 4\% + 1\% = 5\%$।</t>
+          <t>$VC = \frac{0.5\text{ mm}}{25} = 0.02\text{ mm} = 0.002\text{ cm}$। মোট পাঠ $= 4.15 + 17 \times 0.002 = 4.184\text{ cm}$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>$\pm 5\%$</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>পরিমাপ $L = 4.184\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4185,40 +3923,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>মাত্রাগত সমীকরণের ধ্রুবকের মাত্রা ও একক</t>
+          <t>স্লাইড ক্যালিপার্স ও ভার্নিয়ার ধ্রুবক</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ভ্যান ডার ওয়ালস সমীকরণ $\left(P + \frac{a}{V^2}\right)(V - b) = RT$-এ $P$ চাপ এবং $V$ মোলার আয়তন নির্দেশ করলে ধ্রুবক $a$ এবং $b$-এর মাত্রা ও SI একক নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:cube[s=4][size:small]##
+একটি ঘনকের আয়তন পরিমাপে বাহুর দৈর্ঘ্য মাপা হলো স্লাইড ক্যালিপার্সে। মূল স্কেল পাঠ $8.5\text{ cm}$, ভার্নিয়ার সমপাতন $6$, $VC = 0.01\text{ cm}$ এবং ঋণাত্মক ত্রুটি $-0.04\text{ cm}$ হলে ঘনকের সমগ্র তলের ক্ষেত্রফল কত?</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:cube[s=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>সমমাত্রিকতা নীতি অনুসারে, চাপের সাথে কেবল চাপই যোগ করা যায়:
-$[P] = \left[\frac{a}{V^2}\right] \implies [a] = [P][V^2] = [ML^{-1}T^{-2}][L^6] = [ML^5 T^{-2}]$।
-একক: $\text{N/m}^2 \times (\text{{m}}^3)^2 = \text{{N}}\cdot\text{{m}}^4$ (মোল এককে $\text{{N}}\cdot\text{{m}}^4\text{{mol}}^{-2}$)।
-অনুরূপভাবে, আয়তন থেকে আয়তন বিয়োগ হয়: $[b] = [V] = [L^3]$, একক: $\text{{m}}^3\text{{mol}}^{-1}$।</t>
+          <t>প্রকৃত বাহু $a = (8.5 + 6 \times 0.01) - (-0.04) = 8.56 + 0.04 = 8.60\text{ cm}$। সমগ্র তলের ক্ষেত্রফল $A = 6a^2 = 6(8.60)^2 = 443.76 \approx 443.8\text{ cm}^2$ (সঠিক হিসাব: $6 \times 73.96 = 443.76\text{ cm}^2$)।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>$[a] = [ML^5 T^{-2}], \text{SI: }\text{{N}}\cdot\text{{m}}^4/\text{{mol}}^2$; $[b] = [L^3], \text{SI: }\text{{m}}^3/\text{{mol}}$</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>সমগ্রতলের ক্ষেত্রফল $A = 469.8\text{ cm}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4238,7 +3974,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>কৈশিক নলে সান্দ্র তরলের প্রবাহ ও মাত্রীয় বিশ্লেষণ</t>
+          <t>স্লাইড ক্যালিপার্স ও ভার্নিয়ার ধ্রুবক</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4251,30 +3987,25 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=7][size:small]##
-পয়েসিলির সূত্রানুসারে প্রতি সেকেন্ডে কৈশিক নল দিয়ে নির্গত তরলের আয়তন $V = \frac{\pi P r^4}{8 \eta l}$। কোনো পরীক্ষায় চাপের পার্থক্য $P$ পরিমাপে $1.5\%$, ব্যাসার্ধ $r$ পরিমাপে $1.2\%$, এবং দৈর্ঘ্য $l$ পরিমাপে $0.8\%$ ত্রুটি থাকলে তরলের সান্দ্রতা গুণাঙ্ক $\eta$ নির্ণয়ে সম্ভাব্য সর্বোচ্চ ত্রুটির হার কত?</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি ধাতব তারের ব্যাস স্লাইড ক্যালিপার্সে পরিমাপ করে পাঠ পাওয়া গেল: মূল স্কেল $1.4\text{ cm}$, ভার্নিয়ার $9$, $VC = 0.005\text{ cm}$। তারটির দৈর্ঘ্য মিটার স্কেলে মেপে $120.0\text{ cm}$ পাওয়া গেলে তারের আয়তন কত?</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=7][size:small]##</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>সূত্রের রূপান্তর: $\eta = \frac{\pi P r^4}{8 V l}$ (যদি $V$-এর পরিমাপে ত্রুটি উপেক্ষা করা হয় বা নির্দিষ্ট ধরা হয়):
-$\frac{\Delta \eta}{\eta} = \frac{\Delta P}{P} + 4\frac{\Delta r}{r} + \frac{\Delta l}{l} = 1.5\% + 4(1.2\%) + 0.8\% = 1.5\% + 4.8\% + 0.8\% = 7.1\%$।</t>
+          <t>ব্যাস $d = 1.4 + 9 \times 0.005 = 1.445\text{ cm}$। ব্যাসার্ধ $r = 0.7225\text{ cm}$। আয়তন $V = \pi r^2 L = \pi (0.7225)^2 \times 120.0 = 196.78\text{ mm}^3 \approx 1.97\text{ cm}^3$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>$7.1\%$</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>আয়তন $V = 1.97\text{ cm}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4294,44 +4025,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>গোলকের পৃষ্ঠটান পরিমাপে ত্রুটি</t>
+          <t>স্লাইড ক্যালিপার্স ও ভার্নিয়ার ধ্রুবক</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>##GEO:circle-radius[r=4][size:small]##
-একটি তরলের পৃষ্ঠটান নির্ণয়ে $T = \frac{r h \rho g}{2}$ সূত্র ব্যবহার করা হয়। কৈশিক নলের ব্যাসার্ধ $r = (0.50 \pm 0.01)\text{{ mm}}$ এবং তরলের আরোহণ $h = (4.00 \pm 0.04)\text{{ cm}}$ পরিমাপ করা হলে $T$-এর মানে শতকরা আপেক্ষিক অনিশ্চয়তা কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি গোলকের ব্যাস পরিমাপে মূল স্কেল পাঠ $3.7\text{ cm}$, ভার্নিয়ার সমপাতন $3$, $VC = 0.01\text{ cm}$ এবং শূন্য ত্রুটি $+0.01\text{ cm}$। ভর সাধারণ তুলায় মেপে $180.5\text{ g}$ পাওয়া গেলে গোলকের উপাদানের ঘনত্ব কত?</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>##GEO:circle-radius[r=4][size:small]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>$\frac{\Delta r}{r} = \frac{0.01}{0.50} = 0.02 = 2\%$।
-$\frac{\Delta h}{h} = \frac{0.04}{4.00} = 0.01 = 1\%$।
-$\therefore \frac{\Delta T}{T} = 2\% + 1\% = 3\%$।</t>
+          <t>ব্যাস $D = (3.7 + 3 \times 0.01) - 0.01 = 3.72\text{ cm}$। ব্যাসার্ধ $R = 1.86\text{ cm}$। আয়তন $V = \frac{4}{3}\pi (1.86)^3 = 26.95\text{ cm}^3$। ঘনত্ব $\rho = \frac{m}{V} = \frac{180.5}{26.95} = 6.70\text{ g/cm}^3$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>$3.0\%$</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>ঘনত্ব $\rho = 6.78\text{ g/cm}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4351,37 +4076,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>প্লাঙ্ক ধ্রুবকের মাত্রা ও ইলেকট্রন ভোল্ট রূপান্তর</t>
+          <t>স্ক্রু গেজ ও স্ফেরোমিটারের সাহায্যে পরিমাপ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>EASY</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>একটি ফোটনের শক্তি $E = 3.2 \times 10^{-19}\text{{ J}}$ এবং কম্পাঙ্ক $f = 4.82 \times 10^{14}\text{{ Hz}}$ হলে প্লাঙ্কের ধ্রুবক $h = E/f$-এর মান ও মাত্রা কত?</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি স্ক্রু গেজের পিচ $1\text{ mm}$ এবং বৃত্তাকার স্কেলের মোট ভাগ সংখ্যা $100$। কোনো যান্ত্রিক ত্রুটি নেই। একটি সরু তারের ব্যাস পরিমাপে রৈখিক স্কেল পাঠ $3\text{ mm}$ এবং বৃত্তাকার স্কেল পাঠ $48$ পাওয়া গেল। তারটির প্রস্থচ্ছেদের ক্ষেত্রফল নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>$h = \frac{3.2 \times 10^{-19}}{4.82 \times 10^{14}} = 6.639 \times 10^{-34}\text{{ J}}\cdot\text{{s}}$। মাত্রা $[E]/[f] = [ML^2 T^{-2}]/[T^{-1}] = [ML^2 T^{-1}]$।</t>
+          <t>লঘিষ্ঠ গণন $LC = \frac{1\text{ mm}}{100} = 0.01\text{ mm}$। ব্যাস $d = 3 + 48 \times 0.01 = 3.48\text{ mm} = 3.48\times 10^{-3}\text{ m}$। ব্যাসার্ধ $r = 1.74\times 10^{-3}\text{ m}$। ক্ষেত্রফল $A = \pi r^2 = \pi (1.74\times 10^{-3})^2 = 9.51\times 10^{-6}\text{ m}^2$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>$6.64 \times 10^{-34}\text{{ J}}\cdot\text{{s}}$, মাত্রা $[ML^2 T^{-1}]$</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>ক্ষেত্রফল $A = 9.51\times 10^{-6}\text{ m}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4401,37 +4127,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>সার্বজনীন মহাকর্ষীয় ধ্রুবক $G$-এর মাত্রা ও একক</t>
+          <t>স্ক্রু গেজ ও স্ফেরোমিটারের সাহায্যে পরিমাপ</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>EASY</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>মহাকর্ষ বল $F = G \frac{m_1 m_2}{r^2}$ থেকে $G$-এর মাত্রা সমীকরণ ও SI একক প্রতিপাদন কর।</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি স্ক্রু গেজের বৃত্তাকার স্কেল একবার সম্পূর্ণ ঘুরালে রৈখিক স্কেল বরাবর $0.5\text{ mm}$ অগ্রসর হয়। বৃত্তাকার স্কেলের ভাগ সংখ্যা $50$। সমতলে স্পর্শ করালে বৃত্তাকার স্কেলের শূন্য দাগ রৈখিক স্কেলের রেফারেন্স রেখার উপরে $4$ ঘর অবস্থান করে (ঋণাত্মক ত্রুটি)। একটি কাচ প্লেটের পুরুত্ব মাপতে রৈখিক পাঠ $2.5\text{ mm}$ এবং বৃত্তাকার পাঠ $32$ হলে প্লেটটির প্রকৃত পুরুত্ব কত?</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>$G = \frac{F r^2}{m_1 m_2} \implies [G] = \frac{[MLT^{-2}][L^2]}{[M^2]} = [M^{-1}L^3 T^{-2}]$।</t>
+          <t>$LC = \frac{0.5\text{ mm}}{50} = 0.01\text{ mm}$। ঋণাত্মক ত্রুটি $e = -4 \times 0.01 = -0.04\text{ mm}$। দৃশ্যমান পাঠ $= 2.5 + 32 \times 0.01 = 2.82\text{ mm}$। প্রকৃত পাঠ $= 2.82 - (-0.04) = 2.86\text{ mm}$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>মাত্রা $[M^{-1} L^3 T^{-2}]$, একক $\text{{N}}\cdot\text{{m}}^2\text{{kg}}^{-2}$</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>প্রকৃত পুরুত্ব $t = 2.86\text{ mm}$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4451,37 +4178,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>তড়িৎ ভেদ্যতা $\epsilon_0$-এর মাত্রা বিশ্লেষণ</t>
+          <t>স্ক্রু গেজ ও স্ফেরোমিটারের সাহায্যে পরিমাপ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>কুলম্বের সূত্র $F = \frac{1}{4\pi \epsilon_0}\frac{q_1 q_2}{r^2}$ থেকে শূন্যস্থানের প্রবেশ্যতা $\epsilon_0$-এর মাত্রা ও একক নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1,h=5][size:small]##
+একটি স্ক্রু গেজে ধনাত্মক শূন্য ত্রুটি $+3$ ভাগ ($LC = 0.01\text{ mm}$)। একটি তামার তারের ব্যাস পরিমাপে রৈখিক স্কেল পাঠ $4\text{ mm}$ এবং বৃত্তাকার পাঠ $65$ পাওয়া গেল। তারটির দৈর্ঘ্য $2\text{ m}$ এবং উপাদানের আপেক্ষিক রোধ $1.7	imes 10^{-8}\ \Omega\text{m}$ হলে তারের বৈদ্যুতিক রোধ কত?</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>$\epsilon_0 = \frac{q^2}{4\pi F r^2} \implies [\epsilon_0] = \frac{[I^2 T^2]}{[MLT^{-2}][L^2]} = [M^{-1}L^{-3}T^4 I^2]$।</t>
+          <t>প্রকৃত ব্যাস $d = 4 + (65 - 3) \times 0.01 = 4.62\text{ mm} = 4.62\times 10^{-3}\text{ m}$। প্রস্থচ্ছেদ $A = \frac{\pi}{4} d^2 = \frac{\pi}{4} (4.62\times 10^{-3})^2 = 1.676\times 10^{-5}\text{ m}^2$। রোধ $R = \rho \frac{L}{A} = \frac{1.7\times 10^{-8} \times 2}{1.676\times 10^{-5}} = 2.03\times 10^{-3}\ \Omega$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>$[M^{-1} L^{-3} T^4 I^2]$, একক $\text{{C}}^2\text{{N}}^{-1}\text{{m}}^{-2}$</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>রোধ $R = 2.03\times 10^{-3}\ \Omega$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4501,37 +4229,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>স্টিফানের ধ্রুবক $\sigma$-এর মাত্রা ও একক</t>
+          <t>স্ক্রু গেজ ও স্ফেরোমিটারের সাহায্যে পরিমাপ</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>স্টিফান-বোল্টজম্যান সূত্র $E = \sigma A T^4 t$ (যেখানে $E$ বিকীর্ণ তাপশক্তি, $A$ ক্ষেত্রফল, $T$ তাপমাত্রা, $t$ সময়) থেকে $\sigma$-এর মাত্রা ও একক বের কর।</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+একটি মাইক্রোমিটার স্ক্রু গেজের পিচ $0.5\text{ mm}$ এবং বৃত্তাকার স্কেলের ভাগ সংখ্যা $100$। একটি চুল বা সরু ফাইবারের ব্যাস মাপতে রৈখিক পাঠ $0.5\text{ mm}$ এবং বৃত্তাকার পাঠ $82$ পাওয়া গেল। ফাইবারটির প্রস্থচ্ছেদের ক্ষেত্রফল মাইক্রোমিটার স্কয়ারে প্রকাশ কর।</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>$\sigma = \frac{E}{A t T^4} \implies [\sigma] = \frac{[ML^2 T^{-2}]}{[L^2][T][\Theta^4]} = [M T^{-3}\Theta^{-4}]$।</t>
+          <t>$LC = \frac{0.5\text{ mm}}{100} = 0.005\text{ mm}$। ব্যাস $d = 0.5 + 82 \times 0.005 = 0.910\text{ mm} = 910\ \mu\text{m}$। ব্যাসার্ধ $r = 455\ \mu\text{m}$। ক্ষেত্রফল $A = \pi (455)^2 \approx 6.50\times 10^5\ \mu\text{m}^2$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>$[M T^{-3} \Theta^{-4}]$, একক $\text{{W}}\cdot\text{{m}}^{-2}\cdot\text{{K}}^{-4}$</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>ক্ষেত্রফল $A = 0.650\text{ mm}^2 = 6.50\times 10^5\ \mu\text{m}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4551,37 +4280,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>সান্দ্রতা গুণাঙ্কের মাত্রা সমীকরণ প্রমাণ</t>
+          <t>স্ক্রু গেজ ও স্ফেরোমিটারের সাহায্যে পরিমাপ</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>EASY</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>স্টোকসের সূত্র $F = 6\pi \eta r v$ ব্যবহার করে সান্দ্রতা গুণাঙ্ক $\eta$-এর মাত্রা ও SI একক নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+স্ফেরোমিটারের তিন পায়ের মধ্যবর্তী গড় দূরত্ব $l = 4.5\text{ cm}$। সমতল কাচপ্লেটে শূন্য পাঠ নেওয়ার পর একটি উত্তল তলে স্থাপন করলে কেন্দ্রীয় স্ক্রুর রৈখিক পাঠ $2\text{ mm}$ এবং বৃত্তাকার পাঠ $24$ ভাগ পাওয়া যায় (পিচ $1\text{ mm}$, বৃত্তাকার ভাগ $50$)। তলটির বক্রতার ব্যাসার্ধ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>$\eta = \frac{F}{6\pi r v} \implies [\eta] = \frac{[MLT^{-2}]}{[L][LT^{-1}]} = [ML^{-1}T^{-1}]$।</t>
+          <t>$LC = \frac{1\text{ mm}}{50} = 0.02\text{ mm}$। উচ্চতা $h = 2 + 24 \times 0.02 = 2.48\text{ mm} = 0.248\text{ cm}$। বক্রতার ব্যাসার্ধ $R = \frac{l^2}{6h} + \frac{h}{2} = \frac{(4.5)^2}{6 \times 0.248} + \frac{0.248}{2} = 13.61 + 0.124 = 13.73\text{ cm}$।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>$[M L^{-1} T^{-1}]$, একক $\text{{Pa}}\cdot\text{{s}}$ বা $\text{{kg}}\cdot\text{{m}}^{-1}\cdot\text{{s}}^{-1}$</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>বক্রতার ব্যাসার্ধ $R = 14.93\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4601,7 +4331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 16</t>
+          <t>স্ক্রু গেজ ও স্ফেরোমিটারের সাহায্যে পরিমাপ</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4610,35 +4340,29 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##
-[সমস্যা 16: স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 16]
-একটি স্ক্রু গজের পিচ $1\text{ mm}$ এবং বৃত্তাকার স্কেলের ভাগসংখ্যা ১০০। শূন্য দাগ রেফারেন্স রেখার ৫ ঘর ওপরে থাকায় ঋণাত্মক ত্রুটি বিদ্যমান। একটি গোলকের ব্যাস মাপতে গিয়ে রৈখিক পাঠ $5\text{ mm}$ এবং বৃত্তাকার পাঠ 46 পাওয়া গেল। ত্রুটিমুক্ত ব্যাস ও আয়তন কত?</t>
+          <t>##GEO:circle[r=2.8][size:small]##
+একটি অবতল দর্পণের বক্রতার ব্যাসার্ধ মাপতে স্ফেরোমিটারের তিন পায়ের গড় দূরত্ব $l = 5.0\text{ cm}$ পাওয়া গেল। স্ক্রুটির উল্লম্ব পাঠ $h = 1.55\text{ mm}$ হলে দর্পণটির ফোকাস দূরত্ব কত?</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##</t>
+          <t>##GEO:circle[r=2.8][size:small]##</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>$LC = 0.01\text{ mm}$। শূন্য ত্রুটি $e = -0.05\text{ mm}$।
-প্রকৃত ব্যাস $d = 5 + 0.46 - (-0.05) = 5.51\text{ mm}$।</t>
+          <t>$h = 0.155\text{ cm}$। $R = \frac{l^2}{6h} + \frac{h}{2} = \frac{25}{6 \times 0.155} + \frac{0.155}{2} = 26.88 + 0.08 = 26.96\text{ cm}$। ফোকাস দূরত্ব $f = \frac{R}{2} = \frac{26.96}{2} = 13.48\text{ cm}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>$5.51\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>ফোকাস দূরত্ব $f = 13.48\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4658,38 +4382,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 17</t>
+          <t>স্ক্রু গেজ ও স্ফেরোমিটারের সাহায্যে পরিমাপ</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 17]
-কোনো গতিশীল বস্তুর ভরবেগ পরিমাপে শতকরা ত্রুটি $\pm 1.5\%$ হলে, বস্তুর গতিশক্তি $E_k = \frac{p^2}{2m}$ গণনায় শতকরা কত ত্রুটি পরিলক্ষিত হবে?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+স্ক্রু গেজে ব্যাকল্যাশ বা পিছট ত্রুটি (Backlash error) এড়াতে র্যাচেট সর্বদা একই দিকে ঘুরানো উচিত। একটি স্ক্রু গেজে ঋণাত্মক পিছট ত্রুটি $-0.05\text{ mm}$। রৈখিক পাঠ $3.5\text{ mm}$ ও বৃত্তাকার পাঠ $40$ ($LC = 0.01\text{ mm}$) হলে সঠিক পাঠ কত?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>$E_k = \frac{p^2}{2m} \implies \frac{\Delta E_k}{E_k} = 2\frac{\Delta p}{p} = 2(1.5\%) = 3.0\%$।</t>
+          <t>পর্যবেক্ষিত পাঠ $= 3.5 + 40 \times 0.01 = 3.90\text{ mm}$। সঠিক পাঠ $= 3.90 - (-0.05) = 3.95\text{ mm}$।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>$\pm 3.0\%$</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>সঠিক পাঠ $d = 3.95\text{ mm}$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4709,7 +4433,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 18</t>
+          <t>স্ক্রু গেজ ও স্ফেরোমিটারের সাহায্যে পরিমাপ</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4718,34 +4442,29 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##
-[সমস্যা 18: সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 18]
-একটি ফাঁপা তামার বেলনের ব্যাসার্ধ পরিমাপে অনিশ্চয়তা $\pm 1.0\%$ এবং উচ্চতা পরিমাপে অনিশ্চয়তা $\pm 1.5\%$। বেলনটির আয়তন নির্ণয়ে সামগ্রিক শতকরা অনিশ্চয়তা কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ইস্পাতের বলের ব্যাস পরিমাপে স্ক্রু গেজের প্রধান স্কেল পাঠ $6\text{ mm}$, বৃত্তাকার স্কেল পাঠ $72$, $LC = 0.01\text{ mm}$ এবং শূন্য ত্রুটি $+0.02\text{ mm}$ হলে বলটির আয়তন কত?</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>$V = \pi r^2 h \implies \frac{\Delta V}{V} = 2\frac{\Delta r}{r} + \frac{\Delta h}{h} = 2(1.0\%) + 1.5\% = 3.5\%$।</t>
+          <t>প্রকৃত ব্যাস $D = 6 + 72 \times 0.01 - 0.02 = 6.70\text{ mm}$। ব্যাসার্ধ $R = 3.35\text{ mm}$। আয়তন $V = \frac{4}{3}\pi R^3 = \frac{4}{3}\pi (3.35)^3 = 157.48\text{ mm}^3$।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>$\pm 3.5\%$</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>আয়তন $V = 155.6\text{ mm}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4765,7 +4484,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 19</t>
+          <t>স্ক্রু গেজ ও স্ফেরোমিটারের সাহায্যে পরিমাপ</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4774,34 +4493,29 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 19]
-একটি ত্বরান্বিত তরল ফোঁটার কম্পাঙ্ক $n$ তরলের পৃষ্ঠটান $T$, ঘনত্ব $\rho$ এবং ব্যাসার্ধ $r$-এর ওপর নির্ভর করে: $n = k T^x \rho^y r^z$। মাত্রাগত সমীকরণ দ্বারা $x, y, z$-এর মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি কাচ লেন্সের বক্রতার ব্যাসার্ধ নির্ণয়ে স্ফেরোমিটারের তিন শীর্ষবিন্দুর দূরত্ব যথাক্রমে $4.0\text{ cm}, 4.1\text{ cm}, 3.9\text{ cm}$ এবং কেন্দ্রীয় স্ক্রুর উত্থান $h = 0.20\text{ cm}$ হলে লেন্সটির ক্ষমতা (বায়ুতে প্রতিসরাঙ্ক $\mu = 1.5$) কত ডায়োপ্টার?</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>$[n] = [T^{-1}]$।
-$[T] = [MT^{-2}], [\rho] = [ML^{-3}], [r] = [L]$।
-$[M^0 L^0 T^{-1}] = [M^{x+y} L^{-3y+z} T^{-2x}]$।
-$-2x = -1 \implies x = 1/2$।
-$x + y = 0 \implies y = -1/2$।
-$-3(-1/2) + z = 0 \implies z = -3/2$।</t>
+          <t>গড় দূরত্ব $l = \frac{4.0+4.1+3.9}{3} = 4.0\text{ cm}$। বক্রতার ব্যাসার্ধ $R = \frac{4.0^2}{6 \times 0.20} + \frac{0.20}{2} = \frac{16}{1.2} + 0.1 = 13.43\text{ cm} = 0.1343\text{ m}$। সমোত্তল লেন্সের ক্ষমতা $P = (\mu - 1)\left(\frac{2}{R}\right) = (0.5)\left(\frac{2}{0.1343}\right) = +7.45\text{ D}$।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>$x = 1/2, y = -1/2, z = -3/2$</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>ক্ষমতা $P = +7.43\text{ D}$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4821,44 +4535,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 20</t>
+          <t>স্ক্রু গেজ ও স্ফেরোমিটারের সাহায্যে পরিমাপ</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##
-[সমস্যা 20: ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 20]
-একটি বিশেষ ল্যাবরেটরি ভার্নিয়ার স্কেলের মূল স্কেলের ক্ষুদ্রতম ঘরের মান $0.5\text{ mm}$। মূল স্কেলের $49$ ঘর ভার্নিয়ারের $50$ ঘরের সমান। একটি পাতলা শিটের পাঠ নেওয়ার সময় মূল স্কেলের পাঠ $12.5\text{ mm}$ এবং ভার্নিয়ার সমপাতন 20 হলে শিটটির সঠিক বেধ কত?</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি পাতলা ধাতব ফয়েলের বেধ পরিমাপে স্ক্রু গেজের বৃত্তাকার স্কেল $36$ ঘর নির্দেশ করে যখন রৈখিক স্কেল $0\text{ mm}$ এ থাকে ($LC = 0.01\text{ mm}$)। এরূপ $50$ টি ফয়েল একত্রে রাখলে মোট পুরুত্ব কত সেন্টিমিটার হবে?</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>$VC = \frac{0.5}{50} = 0.01\text{ mm}$।
-বেধ $= 12.5 + (20 \times 0.01) = 12.7\text{ mm}$।</t>
+          <t>একটি ফয়েলের বেধ $t = 0 + 36 \times 0.01 = 0.36\text{ mm}$। $50$ টি ফয়েলের বেধ $T = 50 \times 0.36\text{ mm} = 18.0\text{ mm} = 1.80\text{ cm}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>$12.7\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>মোট পুরুত্ব $T = 1.80\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4878,7 +4586,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 21</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4887,35 +4595,29 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##
-[সমস্যা 21: স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 21]
-একটি স্ক্রু গজের পিচ $1\text{ mm}$ এবং বৃত্তাকার স্কেলের ভাগসংখ্যা ১০০। শূন্য দাগ রেফারেন্স রেখার ৫ ঘর ওপরে থাকায় ঋণাত্মক ত্রুটি বিদ্যমান। একটি গোলকের ব্যাস মাপতে গিয়ে রৈখিক পাঠ $5\text{ mm}$ এবং বৃত্তাকার পাঠ 51 পাওয়া গেল। ত্রুটিমুক্ত ব্যাস ও আয়তন কত?</t>
+          <t>##GEO:pendulum[angle=15,length=4][size:small]##
+সরল দোলকের দোলনকাল $T$, কার্যকর দৈর্ঘ্য $L$ এবং অভিকর্ষজ ত্বরণ $g$-এর ওপর নির্ভর করে। মাত্রা বিশ্লেষণের সাহায্যে $T = k L^a g^b$ সমীকরণটি প্রতিপাদন কর এবং দেখাও যে $a = 1/2, b = -1/2$।</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##</t>
+          <t>##GEO:pendulum[angle=15,length=4][size:small]##</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>$LC = 0.01\text{ mm}$। শূন্য ত্রুটি $e = -0.05\text{ mm}$।
-প্রকৃত ব্যাস $d = 5 + 0.51 - (-0.05) = 5.56\text{ mm}$।</t>
+          <t>মাত্রা সমীকরণ: $[T] = [L]^a [LT^{-2}]^b = L^{a+b} T^{-2b}$। ঘাত সমীকৃত করে: $a+b = 0$ এবং $-2b = 1 \implies b = -1/2 \implies a = 1/2$। অতএব $T = k\sqrt{\frac{L}{g}}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>$5.56\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>$T = 2\pi\sqrt{\frac{L}{g}}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4935,38 +4637,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 22</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[সমস্যা 22: গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 22]
-কোনো গতিশীল বস্তুর ভরবেগ পরিমাপে শতকরা ত্রুটি $\pm 2.0\%$ হলে, বস্তুর গতিশক্তি $E_k = \frac{p^2}{2m}$ গণনায় শতকরা কত ত্রুটি পরিলক্ষিত হবে?</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>##GEO:circle[r=1.5][size:small]##
+তরল মাধ্যমে পতনশীল ক্ষুদ্র গোলকের ওপর সান্দ্র বল $F$, সান্দ্রতা গুণাঙ্ক $\eta$, গোলকের ব্যাসার্ধ $r$ এবং প্রান্তীয় বেগ $v$-এর ওপর নির্ভর করে। মাত্রা বিশ্লেষণের সাহায্যে স্টোকসের সূত্র $F = 6\pi\eta r v$ এর ঘাতসমূহ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>$E_k = \frac{p^2}{2m} \implies \frac{\Delta E_k}{E_k} = 2\frac{\Delta p}{p} = 2(2.0\%) = 4.0\%$।</t>
+          <t>$[F] = MLT^{-2}$, $[\eta] = ML^{-1}T^{-1}$, $[r] = L$, $[v] = LT^{-1}$। $MLT^{-2} = (ML^{-1}T^{-1})^a (L)^b (LT^{-1})^c = M^a L^{-a+b+c} T^{-a-c}$। সমীকৃত করে: $a = 1$, $-a-c = -2 \implies c = 1$, $-1+b+1 = 1 \implies b = 1$। অতএব $F = k\eta r v$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>$\pm 4.0\%$</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>$F = k \eta r v$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4986,7 +4688,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 23</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4995,34 +4697,29 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##
-[সমস্যা 23: সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 23]
-একটি ফাঁপা তামার বেলনের ব্যাসার্ধ পরিমাপে অনিশ্চয়তা $\pm 2.0\%$ এবং উচ্চতা পরিমাপে অনিশ্চয়তা $\pm 2.0\%$। বেলনটির আয়তন নির্ণয়ে সামগ্রিক শতকরা অনিশ্চয়তা কত?</t>
+          <t>##PRESET:standing-wave[size:small]##
+একটি টানা তারের অনুপ্রস্থ তরঙ্গের বেগ $v$, তারের টান বল $T$ এবং প্রতি একক দৈর্ঘ্যের ভর $\mu$-এর ওপর নির্ভর করে। মাত্রা বিশ্লেষণের সাহায্যে বেগের সমীকরণটি নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##</t>
+          <t>##PRESET:standing-wave[size:small]##</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>$V = \pi r^2 h \implies \frac{\Delta V}{V} = 2\frac{\Delta r}{r} + \frac{\Delta h}{h} = 2(2.0\%) + 2.0\% = 6.0\%$।</t>
+          <t>$[v] = LT^{-1}$, $[T] = MLT^{-2}$, $[\mu] = ML^{-1}$। $LT^{-1} = (MLT^{-2})^a (ML^{-1})^b = M^{a+b} L^{a-b} T^{-2a}$। $a+b = 0 \implies b = -a$; $-2a = -1 \implies a = 1/2, b = -1/2$। অতএব $v \propto \sqrt{\frac{T}{\mu}}$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>$\pm 6.0\%$</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>$v = k\sqrt{\frac{T}{\mu}}$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5042,7 +4739,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 24</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5051,34 +4748,29 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[সমস্যা 24: মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 24]
-একটি ত্বরান্বিত তরল ফোঁটার কম্পাঙ্ক $n$ তরলের পৃষ্ঠটান $T$, ঘনত্ব $\rho$ এবং ব্যাসার্ধ $r$-এর ওপর নির্ভর করে: $n = k T^x \rho^y r^z$। মাত্রাগত সমীকরণ দ্বারা $x, y, z$-এর মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+পৃষ্ঠটান $S$-এর কারণে কৈশিক নলে তরলের উত্থান $h$, নলটির ব্যাসার্ধ $r$, তরলের ঘনত্ব $\rho$ এবং অভিকর্ষজ ত্বরণ $g$-এর ওপর নির্ভরশীল হলে মাত্রা সমীকরণের সাহায্যে $h$-এর নির্ভরশীলতা যাচাই কর।</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>$[n] = [T^{-1}]$।
-$[T] = [MT^{-2}], [\rho] = [ML^{-3}], [r] = [L]$।
-$[M^0 L^0 T^{-1}] = [M^{x+y} L^{-3y+z} T^{-2x}]$।
-$-2x = -1 \implies x = 1/2$।
-$x + y = 0 \implies y = -1/2$।
-$-3(-1/2) + z = 0 \implies z = -3/2$।</t>
+          <t>$[h] = L$, $[S] = MT^{-2}$, $[\rho] = ML^{-3}$, $[g] = LT^{-2}$, $[r] = L$। $L = (MT^{-2})^a (ML^{-3})^b (LT^{-2})^c (L)^d$। সমাধান করে দেখা যায় $h \propto \frac{S}{\rho g r}$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>$x = 1/2, y = -1/2, z = -3/2$</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>$h = k \frac{S}{\rho g r}$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5098,44 +4790,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 25</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##
-[সমস্যা 25: ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 25]
-একটি বিশেষ ল্যাবরেটরি ভার্নিয়ার স্কেলের মূল স্কেলের ক্ষুদ্রতম ঘরের মান $0.5\text{ mm}$। মূল স্কেলের $49$ ঘর ভার্নিয়ারের $50$ ঘরের সমান। একটি পাতলা শিটের পাঠ নেওয়ার সময় মূল স্কেলের পাঠ $12.5\text{ mm}$ এবং ভার্নিয়ার সমপাতন 25 হলে শিটটির সঠিক বেধ কত?</t>
+          <t>##PRESET:standing-wave[size:small]##
+কৈশিক তরঙ্গে তরঙ্গের বেগ $v$ তরঙ্গদৈর্ঘ্য $\lambda$, ঘনত্ব $\rho$ এবং পৃষ্ঠটান $S$-এর ওপর নির্ভর করে। মাত্রা বিশ্লেষণের মাধ্যমে বেগের সমীকরণ প্রতিপাদন কর।</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##</t>
+          <t>##PRESET:standing-wave[size:small]##</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>$VC = \frac{0.5}{50} = 0.01\text{ mm}$।
-বেধ $= 12.5 + (25 \times 0.01) = 12.75\text{ mm}$।</t>
+          <t>$[v] = LT^{-1} = (\lambda)^a (\rho)^b (S)^c = L^a (ML^{-3})^b (MT^{-2})^c = M^{b+c} L^{a-3b} T^{-2c}$। $b+c = 0$, $-2c = -1 \implies c = 1/2, b = -1/2$। $a - 3(-1/2) = 1 \implies a = 1 - 3/2 = -1/2$। অতএব $v = k\sqrt{\frac{S}{\rho\lambda}}$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>$12.75\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>$v = k\sqrt{\frac{S}{\rho \lambda}}$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5155,7 +4841,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 26</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5164,35 +4850,29 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##
-[সমস্যা 26: স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 26]
-একটি স্ক্রু গজের পিচ $1\text{ mm}$ এবং বৃত্তাকার স্কেলের ভাগসংখ্যা ১০০। শূন্য দাগ রেফারেন্স রেখার ৫ ঘর ওপরে থাকায় ঋণাত্মক ত্রুটি বিদ্যমান। একটি গোলকের ব্যাস মাপতে গিয়ে রৈখিক পাঠ $5\text{ mm}$ এবং বৃত্তাকার পাঠ 56 পাওয়া গেল। ত্রুটিমুক্ত ব্যাস ও আয়তন কত?</t>
+          <t>##GEO:circle[r=3.5][size:small]##
+মহাকর্ষীয় ক্ষেত্রে একটি উপগ্রহের কক্ষীয় বেগ $v$, পৃথিবীর ভর $M$, কক্ষপথের ব্যাসার্ধ $r$ এবং মহাকর্ষীয় ধ্রুবক $G$-এর ওপর নির্ভর করে। মাত্রা বিশ্লেষণের সাহায্যে কক্ষীয় বেগের রাশিমালা নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##</t>
+          <t>##GEO:circle[r=3.5][size:small]##</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>$LC = 0.01\text{ mm}$। শূন্য ত্রুটি $e = -0.05\text{ mm}$।
-প্রকৃত ব্যাস $d = 5 + 0.56 - (-0.05) = 5.61\text{ mm}$।</t>
+          <t>$[G] = M^{-1}L^3 T^{-2}$, $[M] = M$, $[r] = L$। $[v] = LT^{-1} = (M^{-1}L^3 T^{-2})^a (M)^b (L)^c = M^{-a+b} L^{3a+c} T^{-2a}$। $-2a = -1 \implies a = 1/2$। $-a+b = 0 \implies b = 1/2$। $3(1/2) + c = 1 \implies c = -1/2$। অতএব $v = k\sqrt{\frac{GM}{r}}$।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>$5.61\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>$v = k\sqrt{\frac{GM}{r}}$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5212,38 +4892,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 27</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 27]
-কোনো গতিশীল বস্তুর ভরবেগ পরিমাপে শতকরা ত্রুটি $\pm 2.5\%$ হলে, বস্তুর গতিশক্তি $E_k = \frac{p^2}{2m}$ গণনায় শতকরা কত ত্রুটি পরিলক্ষিত হবে?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=2][size:small]##
+ভ্যান ডার ওয়ালস সমীকরণ $\left(P + \frac{a}{V^2}\right)(V - b) = RT$-এ ধ্রুবক $a$ এবং $b$-এর মাত্রা এবং এসআই একক নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>$E_k = \frac{p^2}{2m} \implies \frac{\Delta E_k}{E_k} = 2\frac{\Delta p}{p} = 2(2.5\%) = 5.0\%$।</t>
+          <t>মাত্রাগত সমসত্ত্বতার নীতি অনুসারে: $[b] = [V] = L^3$। আবার $\left[\frac{a}{V^2}\right] = [P] = ML^{-1}T^{-2} \implies [a] = [P][V]^2 = (ML^{-1}T^{-2})(L^6) = ML^5 T^{-2}$। এসআই একক $\text{N}\cdot\text{m}^4$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>$\pm 5.0\%$</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>$[a] = ML^5 T^{-2}\ (\text{N}\cdot\text{m}^4), [b] = L^3\ (\text{m}^3)$</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5263,7 +4943,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 28</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5272,34 +4952,29 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##
-[সমস্যা 28: সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 28]
-একটি ফাঁপা তামার বেলনের ব্যাসার্ধ পরিমাপে অনিশ্চয়তা $\pm 1.5\%$ এবং উচ্চতা পরিমাপে অনিশ্চয়তা $\pm 1.5\%$। বেলনটির আয়তন নির্ণয়ে সামগ্রিক শতকরা অনিশ্চয়তা কত?</t>
+          <t>##GEO:circle[r=2][size:small]##
+একটি বুদবুদের প্রসারণে কম্পাঙ্ক $\nu$, বুদবুদের চাপ $P$, ঘনত্ব $\rho$ এবং মোট শক্তি $E$-এর ওপর নির্ভর করে। মাত্রা বিশ্লেষণের সাহায্যে কম্পাঙ্কের সূত্র নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##</t>
+          <t>##GEO:circle[r=2][size:small]##</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>$V = \pi r^2 h \implies \frac{\Delta V}{V} = 2\frac{\Delta r}{r} + \frac{\Delta h}{h} = 2(1.5\%) + 1.5\% = 4.5\%$।</t>
+          <t>$[\nu] = T^{-1}$, $[P] = ML^{-1}T^{-2}$, $[\rho] = ML^{-3}$, $[E] = ML^2 T^{-2}$। ঘাত সমীকৃত করে তিনটি অজানা মান সমাধান করা হয়।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>$\pm 4.5\%$</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>$\nu = k P^{5/6} \rho^{-1/2} E^{-1/3}$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5319,7 +4994,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 29</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5328,34 +5003,29 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 29]
-একটি ত্বরান্বিত তরল ফোঁটার কম্পাঙ্ক $n$ তরলের পৃষ্ঠটান $T$, ঘনত্ব $\rho$ এবং ব্যাসার্ধ $r$-এর ওপর নির্ভর করে: $n = k T^x \rho^y r^z$। মাত্রাগত সমীকরণ দ্বারা $x, y, z$-এর মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=1][size:small]##
+প্লাঙ্কের ধ্রুবক $h$, আলোর বেগ $c$ এবং মহাকর্ষীয় ধ্রুবক $G$ দ্বারা গঠিত প্লাঙ্ক দৈর্ঘ্যের (Planck length) মাত্রা সমীকরণ প্রতিপাদন কর।</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=1][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>$[n] = [T^{-1}]$।
-$[T] = [MT^{-2}], [\rho] = [ML^{-3}], [r] = [L]$।
-$[M^0 L^0 T^{-1}] = [M^{x+y} L^{-3y+z} T^{-2x}]$।
-$-2x = -1 \implies x = 1/2$।
-$x + y = 0 \implies y = -1/2$।
-$-3(-1/2) + z = 0 \implies z = -3/2$।</t>
+          <t>$[h] = ML^2 T^{-1}$, $[c] = LT^{-1}$, $[G] = M^{-1}L^3 T^{-2}$। $L = (h)^a (c)^b (G)^c$। $M^{a-c} L^{2a+b+3c} T^{-a-b-2c} = L$। $a - c = 0 \implies a = c$। $-a-b-2a = 0 \implies b = -3a$। $2a - 3a + 3a = 1 \implies 2a = 1 \implies a = 1/2, c = 1/2, b = -3/2$। $l_p = \sqrt{\frac{Gh}{c^3}}$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>$x = 1/2, y = -1/2, z = -3/2$</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>$l_p = \sqrt{\frac{Gh}{c^3}} \approx 1.62\times 10^{-35}\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5375,44 +5045,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 30</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##
-[সমস্যা 30: ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 30]
-একটি বিশেষ ল্যাবরেটরি ভার্নিয়ার স্কেলের মূল স্কেলের ক্ষুদ্রতম ঘরের মান $0.5\text{ mm}$। মূল স্কেলের $49$ ঘর ভার্নিয়ারের $50$ ঘরের সমান। একটি পাতলা শিটের পাঠ নেওয়ার সময় মূল স্কেলের পাঠ $12.5\text{ mm}$ এবং ভার্নিয়ার সমপাতন 30 হলে শিটটির সঠিক বেধ কত?</t>
+          <t>##PRESET:electric-field[size:small]##
+তড়িৎ ক্ষেত্রে শক্তি ঘনত্ব $u = \frac{1}{2}\epsilon_0 E^2$। শূন্য মাধ্যমের ভেদনযোগ্যতা $\epsilon_0$-এর মাত্রা সমীকরণ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##</t>
+          <t>##PRESET:electric-field[size:small]##</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>$VC = \frac{0.5}{50} = 0.01\text{ mm}$।
-বেধ $= 12.5 + (30 \times 0.01) = 12.8\text{ mm}$।</t>
+          <t>কুলম্বের সূত্র: $F = \frac{1}{4\pi\epsilon_0}\frac{q^2}{r^2} \implies \epsilon_0 = \frac{q^2}{F r^2}$। $[\epsilon_0] = \frac{A^2 T^2}{(MLT^{-2})(L^2)} = M^{-1}L^{-3}T^4 A^2$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>$12.8\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>$[\epsilon_0] = M^{-1}L^{-3}T^4 A^2$</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5432,7 +5096,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 31</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5441,35 +5105,29 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##
-[সমস্যা 31: স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 31]
-একটি স্ক্রু গজের পিচ $1\text{ mm}$ এবং বৃত্তাকার স্কেলের ভাগসংখ্যা ১০০। শূন্য দাগ রেফারেন্স রেখার ৫ ঘর ওপরে থাকায় ঋণাত্মক ত্রুটি বিদ্যমান। একটি গোলকের ব্যাস মাপতে গিয়ে রৈখিক পাঠ $5\text{ mm}$ এবং বৃত্তাকার পাঠ 61 পাওয়া গেল। ত্রুটিমুক্ত ব্যাস ও আয়তন কত?</t>
+          <t>##GEO:circle[r=2.2][size:small]##
+একটি দোদুল্যমান তরল ফোঁটার কম্পাঙ্ক $f$, ফোঁটার ব্যাসার্ধ $r$, ঘনত্ব $\rho$ এবং পৃষ্ঠটান $S$-এর ওপর নির্ভর করে। মাত্রা বিশ্লেষণের সাহায্যে দেখাও যে $f \propto \sqrt{\frac{S}{\rho r^3}}$।</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##</t>
+          <t>##GEO:circle[r=2.2][size:small]##</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>$LC = 0.01\text{ mm}$। শূন্য ত্রুটি $e = -0.05\text{ mm}$।
-প্রকৃত ব্যাস $d = 5 + 0.61 - (-0.05) = 5.66\text{ mm}$।</t>
+          <t>$[f] = T^{-1} = (r)^a (\rho)^b (S)^c = L^a (ML^{-3})^b (MT^{-2})^c$। সমীকৃত করে: $b+c = 0$, $-2c = -1 \implies c = 1/2, b = -1/2$। $a - 3(-1/2) = 0 \implies a = -3/2$। অতএব $f = k\sqrt{\frac{S}{\rho r^3}}$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>$5.66\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>$f = k\sqrt{\frac{S}{\rho r^3}}$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5489,38 +5147,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 32</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[সমস্যা 32: গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 32]
-কোনো গতিশীল বস্তুর ভরবেগ পরিমাপে শতকরা ত্রুটি $\pm 1.0\%$ হলে, বস্তুর গতিশক্তি $E_k = \frac{p^2}{2m}$ গণনায় শতকরা কত ত্রুটি পরিলক্ষিত হবে?</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+মহাজাগতিক কৃষ্ণগহ্বরের স্টিফেন-হকিং বিকিরণ তাপমাত্রা $T$, প্লাঙ্কের হ্রাসকৃত ধ্রুবক $\hbar$, আলোর বেগ $c$, বোল্টজম্যান ধ্রুবক $k_B$, মহাকর্ষীয় ধ্রুবক $G$ এবং ব্ল্যাকহোলের ভর $M$-এর ওপর নির্ভর করে। মাত্রা বিশ্লেষণের সাহায্যে দেখাও যে $T \propto \frac{\hbar c^3}{G M k_B}$।</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>$E_k = \frac{p^2}{2m} \implies \frac{\Delta E_k}{E_k} = 2\frac{\Delta p}{p} = 2(1.0\%) = 2.0\%$।</t>
+          <t>উভয়পক্ষের মৌলিক মাত্রা $M, L, T, K$ সমীকৃত করে হকিং তাপমাত্রার ব্যাস্তানুপাতিক সম্পর্ক প্রমাণিত হয়।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>$\pm 2.0\%$</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>$T = k \frac{\hbar c^3}{G M k_B}$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5540,7 +5198,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 33</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5549,34 +5207,29 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##
-[সমস্যা 33: সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 33]
-একটি ফাঁপা তামার বেলনের ব্যাসার্ধ পরিমাপে অনিশ্চয়তা $\pm 1.0\%$ এবং উচ্চতা পরিমাপে অনিশ্চয়তা $\pm 2.0\%$। বেলনটির আয়তন নির্ণয়ে সামগ্রিক শতকরা অনিশ্চয়তা কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ঘূর্ণায়মান ডিস্কের কেন্দ্রমুখী ত্বরণ $a_c$ ব্যাসার্ধ $r$ এবং কৌণিক বেগ $\omega$-এর ওপর নির্ভর করে। মাত্রা বিশ্লেষণের সাহায্যে $a_c = r \omega^2$ সম্পর্কটি প্রতিপাদন কর।</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>$V = \pi r^2 h \implies \frac{\Delta V}{V} = 2\frac{\Delta r}{r} + \frac{\Delta h}{h} = 2(1.0\%) + 2.0\% = 4.0\%$।</t>
+          <t>$[a_c] = LT^{-2}$, $[r] = L$, $[\omega] = T^{-1}$। $LT^{-2} = L^a (T^{-1})^b = L^a T^{-b} \implies a = 1, b = 2$। অতএব $a_c = r\omega^2$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>$\pm 4.0\%$</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>$a_c = r\omega^2$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5596,7 +5249,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 34</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5605,34 +5258,29 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[সমস্যা 34: মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 34]
-একটি ত্বরান্বিত তরল ফোঁটার কম্পাঙ্ক $n$ তরলের পৃষ্ঠটান $T$, ঘনত্ব $\rho$ এবং ব্যাসার্ধ $r$-এর ওপর নির্ভর করে: $n = k T^x \rho^y r^z$। মাত্রাগত সমীকরণ দ্বারা $x, y, z$-এর মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:circle[r=1.8][size:small]##
+সান্দ্র মাধ্যমে স্থির বেগে চলমান একটি গোলকের ক্ষমতা $P$, সান্দ্রতা গুণাঙ্ক $\eta$, গোলকের ব্যাসার্ধ $r$ এবং বেগ $v$-এর ওপর নির্ভরশীল। মাত্রা বিশ্লেষণের সাহায্যে ক্ষমতার সমীকরণ প্রতিপাদন কর।</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=1.8][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>$[n] = [T^{-1}]$।
-$[T] = [MT^{-2}], [\rho] = [ML^{-3}], [r] = [L]$।
-$[M^0 L^0 T^{-1}] = [M^{x+y} L^{-3y+z} T^{-2x}]$।
-$-2x = -1 \implies x = 1/2$।
-$x + y = 0 \implies y = -1/2$।
-$-3(-1/2) + z = 0 \implies z = -3/2$।</t>
+          <t>$[P] = ML^2 T^{-3} = (\eta)^a (r)^b (v)^c = (ML^{-1}T^{-1})^a (L)^b (LT^{-1})^c$। $a = 1$, $-1+b+c = 2$, $-1-c = -3 \implies c = 2 \implies b = 1$। অতএব $P = 6\pi \eta r v^2$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>$x = 1/2, y = -1/2, z = -3/2$</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>$P = k \eta r v^2$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5652,44 +5300,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 35</t>
+          <t>মাত্রা বিশ্লেষণ ও সমীকরণের যথার্থতা যাচাই</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##
-[সমস্যা 35: ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 35]
-একটি বিশেষ ল্যাবরেটরি ভার্নিয়ার স্কেলের মূল স্কেলের ক্ষুদ্রতম ঘরের মান $0.5\text{ mm}$। মূল স্কেলের $49$ ঘর ভার্নিয়ারের $50$ ঘরের সমান। একটি পাতলা শিটের পাঠ নেওয়ার সময় মূল স্কেলের পাঠ $12.5\text{ mm}$ এবং ভার্নিয়ার সমপাতন 35 হলে শিটটির সঠিক বেধ কত?</t>
+          <t>##PRESET:standing-wave[size:small]##
+শব্দের বেগ $v$, মাধ্যমের চাপ $P$ এবং ঘনত্ব $\rho$-এর ওপর নির্ভর করে। নিউটনের মাত্রা বিশ্লেষণ অনুসারে $v = k\sqrt{\frac{P}{\rho}}$ সমীকরণটি প্রতিপাদন কর।</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##</t>
+          <t>##PRESET:standing-wave[size:small]##</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>$VC = \frac{0.5}{50} = 0.01\text{ mm}$।
-বেধ $= 12.5 + (35 \times 0.01) = 12.85\text{ mm}$।</t>
+          <t>$[v] = LT^{-1}$, $[P] = ML^{-1}T^{-2}$, $[\rho] = ML^{-3}$। $LT^{-1} = (ML^{-1}T^{-2})^a (ML^{-3})^b = M^{a+b} L^{-a-3b} T^{-2a}$। $-2a = -1 \implies a = 1/2$। $a+b = 0 \implies b = -1/2$। অতএব $v \propto \sqrt{\frac{P}{\rho}}$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>$12.85\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>$v = \sqrt{\frac{P}{\rho}}$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5709,7 +5351,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 36</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5718,35 +5360,29 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##
-[সমস্যা 36: স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 36]
-একটি স্ক্রু গজের পিচ $1\text{ mm}$ এবং বৃত্তাকার স্কেলের ভাগসংখ্যা ১০০। শূন্য দাগ রেফারেন্স রেখার ৫ ঘর ওপরে থাকায় ঋণাত্মক ত্রুটি বিদ্যমান। একটি গোলকের ব্যাস মাপতে গিয়ে রৈখিক পাঠ $5\text{ mm}$ এবং বৃত্তাকার পাঠ 66 পাওয়া গেল। ত্রুটিমুক্ত ব্যাস ও আয়তন কত?</t>
+          <t>##GEO:cube[s=3.5][size:small]##
+একটি ঘনকের বাহুর পরিমাপে শতকরা ত্রুটি $1.5\%$ এবং ভরের পরিমাপে শতকরা ত্রুটি $2.0\%$। ঘনকটির উপাদানের ঘনত্ব নির্ণয়ে সর্বোচ্চ সম্ভাব্য শতকরা ত্রুটি কত?</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##</t>
+          <t>##GEO:cube[s=3.5][size:small]##</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>$LC = 0.01\text{ mm}$। শূন্য ত্রুটি $e = -0.05\text{ mm}$।
-প্রকৃত ব্যাস $d = 5 + 0.66 - (-0.05) = 5.71\text{ mm}$।</t>
+          <t>ঘনত্ব $\rho = \frac{m}{V} = \frac{m}{a^3}$। আপেক্ষিক ত্রুটি $\frac{\Delta\rho}{\rho} = \frac{\Delta m}{m} + 3\frac{\Delta a}{a}$। শতকরা ত্রুটি $= 2.0\% + 3(1.5\%) = 2.0\% + 4.5\% = 6.5\%$।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>$5.71\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>ঘনত্বে সর্বোচ্চ ত্রুটি $\pm 6.5\%$</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5766,38 +5402,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 37</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 37]
-কোনো গতিশীল বস্তুর ভরবেগ পরিমাপে শতকরা ত্রুটি $\pm 1.5\%$ হলে, বস্তুর গতিশক্তি $E_k = \frac{p^2}{2m}$ গণনায় শতকরা কত ত্রুটি পরিলক্ষিত হবে?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি গোলকের ব্যাসার্ধ পরিমাপে শতকরা ত্রুটি $2\%$ হলে এর পৃষ্ঠের ক্ষেত্রফল এবং আয়তন পরিমাপে শতকরা ত্রুটি যথাক্রমে কত হবে?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>$E_k = \frac{p^2}{2m} \implies \frac{\Delta E_k}{E_k} = 2\frac{\Delta p}{p} = 2(1.5\%) = 3.0\%$।</t>
+          <t>ক্ষেত্রফল $A = 4\pi r^2 \implies \frac{\Delta A}{A} = 2\frac{\Delta r}{r} = 2(2\%) = 4\%$। আয়তন $V = \frac{4}{3}\pi r^3 \implies \frac{\Delta V}{V} = 3\frac{\Delta r}{r} = 3(2\%) = 6\%$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>$\pm 3.0\%$</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>ক্ষেত্রফলে ত্রুটি $4\%$, আয়তনে ত্রুটি $6\%$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5817,7 +5453,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 38</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5826,34 +5462,29 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##
-[সমস্যা 38: সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 38]
-একটি ফাঁপা তামার বেলনের ব্যাসার্ধ পরিমাপে অনিশ্চয়তা $\pm 2.0\%$ এবং উচ্চতা পরিমাপে অনিশ্চয়তা $\pm 1.5\%$। বেলনটির আয়তন নির্ণয়ে সামগ্রিক শতকরা অনিশ্চয়তা কত?</t>
+          <t>##GEO:pendulum[angle=12,length=4][size:small]##
+সরল দোলকের সাহায্যে অভিকর্ষজ ত্বরণ $g$ নির্ণয়ে সুতার দৈর্ঘ্য পরিমাপে শতকরা ত্রুটি $1\%$ এবং দোলনকাল পরিমাপে শতকরা ত্রুটি $1.5\%$ হলে $g$ এর মানে শতকরা ত্রুটি কত?</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##</t>
+          <t>##GEO:pendulum[angle=12,length=4][size:small]##</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>$V = \pi r^2 h \implies \frac{\Delta V}{V} = 2\frac{\Delta r}{r} + \frac{\Delta h}{h} = 2(2.0\%) + 1.5\% = 5.5\%$।</t>
+          <t>$T = 2\pi\sqrt{\frac{L}{g}} \implies g = 4\pi^2 \frac{L}{T^2}$। $\frac{\Delta g}{g} = \frac{\Delta L}{L} + 2\frac{\Delta T}{T} = 1\% + 2(1.5\%) = 1\% + 3\% = 4\%$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>$\pm 5.5\%$</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>$g$ এর মানে শতকরা ত্রুটি $4\%$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5873,7 +5504,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 39</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5882,34 +5513,29 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 39]
-একটি ত্বরান্বিত তরল ফোঁটার কম্পাঙ্ক $n$ তরলের পৃষ্ঠটান $T$, ঘনত্ব $\rho$ এবং ব্যাসার্ধ $r$-এর ওপর নির্ভর করে: $n = k T^x \rho^y r^z$। মাত্রাগত সমীকরণ দ্বারা $x, y, z$-এর মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+ওহমের সূত্র পরীক্ষার সময় একটি পরিবাহীর দুই প্রান্তের বিভব পার্থক্য পরিমাপে পাঠ $V = (100 \pm 2)\text{ V}$ এবং তড়িৎ প্রবাহ $I = (10 \pm 0.2)\text{ A}$ পাওয়া গেল। পরিবাহীটির রোধ $R$ এবং এতে সর্বোচ্চ সম্ভাব্য পরম ত্রুটি ও শতকরা ত্রুটি কত?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>$[n] = [T^{-1}]$।
-$[T] = [MT^{-2}], [\rho] = [ML^{-3}], [r] = [L]$।
-$[M^0 L^0 T^{-1}] = [M^{x+y} L^{-3y+z} T^{-2x}]$।
-$-2x = -1 \implies x = 1/2$।
-$x + y = 0 \implies y = -1/2$।
-$-3(-1/2) + z = 0 \implies z = -3/2$।</t>
+          <t>$R = \frac{V}{I} = \frac{100}{10} = 10\ \Omega$। $\frac{\Delta R}{R} = \frac{\Delta V}{V} + \frac{\Delta I}{I} = \frac{2}{100} + \frac{0.2}{10} = 0.02 + 0.02 = 0.04\ (4\%)$। পরম ত্রুটি $\Delta R = 10 \times 0.04 = 0.4\ \Omega$।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>$x = 1/2, y = -1/2, z = -3/2$</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>$R = (10.0 \pm 0.4)\ \Omega\ (4\%)$</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5929,44 +5555,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 40</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##
-[সমস্যা 40: ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 40]
-একটি বিশেষ ল্যাবরেটরি ভার্নিয়ার স্কেলের মূল স্কেলের ক্ষুদ্রতম ঘরের মান $0.5\text{ mm}$। মূল স্কেলের $49$ ঘর ভার্নিয়ারের $50$ ঘরের সমান। একটি পাতলা শিটের পাঠ নেওয়ার সময় মূল স্কেলের পাঠ $12.5\text{ mm}$ এবং ভার্নিয়ার সমপাতন 40 হলে শিটটির সঠিক বেধ কত?</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি সিলিন্ডারের ব্যাসার্ধ $r = (2.0 \pm 0.1)\text{ cm}$ এবং উচ্চতা $h = (10.0 \pm 0.2)\text{ cm}$। সিলিন্ডারটির আয়তন পরিমাপে শতকরা ত্রুটি নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>$VC = \frac{0.5}{50} = 0.01\text{ mm}$।
-বেধ $= 12.5 + (40 \times 0.01) = 12.9\text{ mm}$।</t>
+          <t>$V = \pi r^2 h$। $\frac{\Delta V}{V} = 2\frac{\Delta r}{r} + \frac{\Delta h}{h} = 2\left(\frac{0.1}{2.0}\right) + \frac{0.2}{10.0} = 2(0.05) + 0.02 = 0.10 + 0.02 = 0.12 = 12\%$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>$12.9\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>আয়তনে শতকরা ত্রুটি $12\%$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5986,7 +5606,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 41</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5995,35 +5615,29 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##
-[সমস্যা 41: স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 41]
-একটি স্ক্রু গজের পিচ $1\text{ mm}$ এবং বৃত্তাকার স্কেলের ভাগসংখ্যা ১০০। শূন্য দাগ রেফারেন্স রেখার ৫ ঘর ওপরে থাকায় ঋণাত্মক ত্রুটি বিদ্যমান। একটি গোলকের ব্যাস মাপতে গিয়ে রৈখিক পাঠ $5\text{ mm}$ এবং বৃত্তাকার পাঠ 71 পাওয়া গেল। ত্রুটিমুক্ত ব্যাস ও আয়তন কত?</t>
+          <t>##GEO:rect[w=3,h=2][size:small]##
+একটি ভৌত রাশি $X = rac{A^2 B^3}{C \sqrt{D}}$। রাশিগুলোতে শতকরা ত্রুটি যথাক্রমে $A: 1\%$, $B: 2\%$, $C: 3\%$, $D: 4\%$ হলে $X$-এর পরিমাপে সর্বোচ্চ শতকরা ত্রুটি কত?</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##</t>
+          <t>##GEO:rect[w=3,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>$LC = 0.01\text{ mm}$। শূন্য ত্রুটি $e = -0.05\text{ mm}$।
-প্রকৃত ব্যাস $d = 5 + 0.71 - (-0.05) = 5.76\text{ mm}$।</t>
+          <t>$\frac{\Delta X}{X} = 2\frac{\Delta A}{A} + 3\frac{\Delta B}{B} + \frac{\Delta C}{C} + \frac{1}{2}\frac{\Delta D}{D} = 2(1\%) + 3(2\%) + 3\% + \frac{1}{2}(4\%) = 2\% + 6\% + 3\% + 2\% = 13\%$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>$5.76\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>$X$-এ সর্বোচ্চ শতকরা ত্রুটি $13\%$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6043,38 +5657,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 42</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[সমস্যা 42: গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 42]
-কোনো গতিশীল বস্তুর ভরবেগ পরিমাপে শতকরা ত্রুটি $\pm 2.0\%$ হলে, বস্তুর গতিশক্তি $E_k = \frac{p^2}{2m}$ গণনায় শতকরা কত ত্রুটি পরিলক্ষিত হবে?</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>##GEO:circle[r=1.8][size:small]##
+একটি বস্তুর ভর $m = (50.0 \pm 0.5)\text{ g}$ এবং বেগ $v = (20.0 \pm 0.4)\text{ m/s}$ হলে বস্তুটির গতিশক্তি পরিমাপে শতকরা ত্রুটি কত?</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=1.8][size:small]##</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>$E_k = \frac{p^2}{2m} \implies \frac{\Delta E_k}{E_k} = 2\frac{\Delta p}{p} = 2(2.0\%) = 4.0\%$।</t>
+          <t>$K = \frac{1}{2}m v^2$। $\frac{\Delta K}{K} = \frac{\Delta m}{m} + 2\frac{\Delta v}{v} = \frac{0.5}{50.0} + 2\left(\frac{0.4}{20.0}\right) = 0.01 + 2(0.02) = 0.01 + 0.04 = 0.05 = 5.0\%$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>$\pm 4.0\%$</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>গতিশক্তিতে শতকরা ত্রুটি $5.0\%$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6094,7 +5708,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 43</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6103,34 +5717,29 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##
-[সমস্যা 43: সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 43]
-একটি ফাঁপা তামার বেলনের ব্যাসার্ধ পরিমাপে অনিশ্চয়তা $\pm 1.5\%$ এবং উচ্চতা পরিমাপে অনিশ্চয়তা $\pm 2.0\%$। বেলনটির আয়তন নির্ণয়ে সামগ্রিক শতকরা অনিশ্চয়তা কত?</t>
+          <t>##GEO:cylinder[r=1,h=5][size:small]##
+একটি তারের ইয়ং-এর গুণাঙ্ক $Y = rac{F L}{\pi r^2 l}$। বল $F$-এ ত্রুটি $1\%$, দৈর্ঘ্য $L$-এ ত্রুটি $0.5\%$, ব্যাসার্ধ $r$-এ ত্রুটি $1.5\%$ এবং প্রসারণ $l$-এ ত্রুটি $2\%$ হলে $Y$-এর শতকরা অনিশ্চয়তা কত?</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##</t>
+          <t>##GEO:cylinder[r=1,h=5][size:small]##</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>$V = \pi r^2 h \implies \frac{\Delta V}{V} = 2\frac{\Delta r}{r} + \frac{\Delta h}{h} = 2(1.5\%) + 2.0\% = 5.0\%$।</t>
+          <t>$\frac{\Delta Y}{Y} = \frac{\Delta F}{F} + \frac{\Delta L}{L} + 2\frac{\Delta r}{r} + \frac{\Delta l}{l} = 1\% + 0.5\% + 2(1.5\%) + 2\% = 1\% + 0.5\% + 3\% + 2\% = 6.5\%$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>$\pm 5.0\%$</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>$Y$-এ শতকরা অনিশ্চয়তা $6.5\%$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6150,7 +5759,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 44</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6159,34 +5768,29 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[সমস্যা 44: মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 44]
-একটি ত্বরান্বিত তরল ফোঁটার কম্পাঙ্ক $n$ তরলের পৃষ্ঠটান $T$, ঘনত্ব $\rho$ এবং ব্যাসার্ধ $r$-এর ওপর নির্ভর করে: $n = k T^x \rho^y r^z$। মাত্রাগত সমীকরণ দ্বারা $x, y, z$-এর মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+দুটি রোধ $R_1 = (100 \pm 3)\ \Omega$ এবং $R_2 = (200 \pm 4)\ \Omega$ শ্রেণি সমবায়ে যুক্ত করলে তুল্য রোধের পরম ত্রুটি এবং সমান্তরাল সমবায়ে যুক্ত করলে শতকরা ত্রুটি নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>$[n] = [T^{-1}]$।
-$[T] = [MT^{-2}], [\rho] = [ML^{-3}], [r] = [L]$।
-$[M^0 L^0 T^{-1}] = [M^{x+y} L^{-3y+z} T^{-2x}]$।
-$-2x = -1 \implies x = 1/2$।
-$x + y = 0 \implies y = -1/2$।
-$-3(-1/2) + z = 0 \implies z = -3/2$।</t>
+          <t>শ্রেণি সমবায়ে: $R_s = R_1 + R_2 = 300\ \Omega$, $\Delta R_s = \Delta R_1 + \Delta R_2 = 3 + 4 = 7\ \Omega$। সমান্তরাল সমবায়ে: $R_p = \frac{R_1 R_2}{R_1 + R_2} = \frac{20000}{300} = 66.67\ \Omega$। $\frac{\Delta R_p}{R_p^2} = \frac{\Delta R_1}{R_1^2} + \frac{\Delta R_2}{R_2^2} \implies \frac{\Delta R_p}{R_p} = R_p \left(\frac{3}{10000} + \frac{4}{40000}\right) = 66.67(0.0003 + 0.0001) = 66.67 \times 0.0004 \approx 2.67\% \approx 2.33\%$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>$x = 1/2, y = -1/2, z = -3/2$</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>শ্রেণিতে পরম ত্রুটি $\pm 7\ \Omega$, সমান্তরালে শতকরা ত্রুটি $2.33\%$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6206,44 +5810,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 45</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##
-[সমস্যা 45: ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 45]
-একটি বিশেষ ল্যাবরেটরি ভার্নিয়ার স্কেলের মূল স্কেলের ক্ষুদ্রতম ঘরের মান $0.5\text{ mm}$। মূল স্কেলের $49$ ঘর ভার্নিয়ারের $50$ ঘরের সমান। একটি পাতলা শিটের পাঠ নেওয়ার সময় মূল স্কেলের পাঠ $12.5\text{ mm}$ এবং ভার্নিয়ার সমপাতন 45 হলে শিটটির সঠিক বেধ কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি গোলকের পৃষ্ঠতলের ক্ষেত্রফল পরিমাপে সর্বোচ্চ শতকরা ত্রুটি $6\%$ হলে এর আয়তন পরিমাপে সর্বোচ্চ শতকরা ত্রুটি কত হবে?</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>$VC = \frac{0.5}{50} = 0.01\text{ mm}$।
-বেধ $= 12.5 + (45 \times 0.01) = 12.95\text{ mm}$।</t>
+          <t>$A = 4\pi r^2 \implies \frac{\Delta A}{A} = 2\frac{\Delta r}{r} = 6\% \implies \frac{\Delta r}{r} = 3\%$। আয়তন $V = \frac{4}{3}\pi r^3 \implies \frac{\Delta V}{V} = 3\frac{\Delta r}{r} = 3(3\%) = 9\%$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>$12.95\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>আয়তনে শতকরা ত্রুটি $9\%$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6263,7 +5861,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 46</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6272,35 +5870,29 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##
-[সমস্যা 46: স্ক্রু গজের সাহায্যে গোলকের ব্যাস ও ত্রুটি 46]
-একটি স্ক্রু গজের পিচ $1\text{ mm}$ এবং বৃত্তাকার স্কেলের ভাগসংখ্যা ১০০। শূন্য দাগ রেফারেন্স রেখার ৫ ঘর ওপরে থাকায় ঋণাত্মক ত্রুটি বিদ্যমান। একটি গোলকের ব্যাস মাপতে গিয়ে রৈখিক পাঠ $5\text{ mm}$ এবং বৃত্তাকার পাঠ 76 পাওয়া গেল। ত্রুটিমুক্ত ব্যাস ও আয়তন কত?</t>
+          <t>##GEO:cube[s=3][size:small]##
+একটি আয়তাকার ব্লকের দৈর্ঘ্য $l = (12.5 \pm 0.1)\text{ cm}$, প্রস্থ $w = (6.0 \pm 0.1)\text{ cm}$ এবং উচ্চতা $h = (3.0 \pm 0.1)\text{ cm}$ হলে ব্লকের আয়তনের মান এবং সম্ভাব্য পরম ত্রুটি কত?</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>##GEO:screw-gauge[size:small]##</t>
+          <t>##GEO:cube[s=3][size:small]##</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>$LC = 0.01\text{ mm}$। শূন্য ত্রুটি $e = -0.05\text{ mm}$।
-প্রকৃত ব্যাস $d = 5 + 0.76 - (-0.05) = 5.81\text{ mm}$।</t>
+          <t>$V = 12.5 \times 6.0 \times 3.0 = 225.0\text{ cm}^3$। $\frac{\Delta V}{V} = \frac{0.1}{12.5} + \frac{0.1}{6.0} + \frac{0.1}{3.0} = 0.008 + 0.0167 + 0.0333 = 0.058$। $\Delta V = 225.0 \times 0.058 = 13.05 \approx 13.1\text{ cm}^3$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>$5.81\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>আয়তন $V = (225.0 \pm 13.1)\text{ cm}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6320,38 +5912,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 47</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: গতিশক্তি ও ভরবেগের আপেক্ষিক ত্রুটি 47]
-কোনো গতিশীল বস্তুর ভরবেগ পরিমাপে শতকরা ত্রুটি $\pm 2.5\%$ হলে, বস্তুর গতিশক্তি $E_k = \frac{p^2}{2m}$ গণনায় শতকরা কত ত্রুটি পরিলক্ষিত হবে?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+একটি ধাতব বলের ব্যাস $d = (10.0 \pm 0.2)\text{ mm}$ এবং ভর $m = (4.15 \pm 0.05)\text{ g}$ হলে ঘনত্বের মান এবং শতকরা ত্রুটি নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>$E_k = \frac{p^2}{2m} \implies \frac{\Delta E_k}{E_k} = 2\frac{\Delta p}{p} = 2(2.5\%) = 5.0\%$।</t>
+          <t>ব্যাসার্ধ $r = 5.0\text{ mm} = 0.5\text{ cm}$। আয়তন $V = \frac{4}{3}\pi (0.5)^3 = 0.5236\text{ cm}^3$। $\rho = \frac{4.15}{0.5236} = 7.926\text{ g/cm}^3$। $\frac{\Delta\rho}{\rho} = \frac{0.05}{4.15} + 3\left(\frac{0.2}{10.0}\right) = 0.012 + 0.060 = 0.072 = 7.2\%$। $\Delta\rho = 7.926 \times 0.072 \approx 0.57\text{ g/cm}^3$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>$\pm 5.0\%$</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>ঘনত্ব $\rho = (7.93 \pm 0.57)\text{ g/cm}^3\ (7.2\%)$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6371,7 +5963,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 48</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6380,34 +5972,29 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##
-[সমস্যা 48: সিলিন্ডারের আয়তনে ত্রুটির বিস্তার 48]
-একটি ফাঁপা তামার বেলনের ব্যাসার্ধ পরিমাপে অনিশ্চয়তা $\pm 1.0\%$ এবং উচ্চতা পরিমাপে অনিশ্চয়তা $\pm 1.5\%$। বেলনটির আয়তন নির্ণয়ে সামগ্রিক শতকরা অনিশ্চয়তা কত?</t>
+          <t>##GEO:rect[w=3,h=2][size:small]##
+তড়িৎ প্রবাহের তাপীয় ফলে উৎপন্ন তাপ $H = rac{I^2 R t}{J}$। যদি $I$-এ ত্রুটি $2\%$, $R$-এ ত্রুটি $1\%$ এবং $t$-এ ত্রুটি $1\%$ হয়, তবে উৎপন্ন তাপের পরিমাপে শতকরা অনিশ্চয়তা কত?</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=6][size:small]##</t>
+          <t>##GEO:rect[w=3,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>$V = \pi r^2 h \implies \frac{\Delta V}{V} = 2\frac{\Delta r}{r} + \frac{\Delta h}{h} = 2(1.0\%) + 1.5\% = 3.5\%$।</t>
+          <t>$\frac{\Delta H}{H} = 2\frac{\Delta I}{I} + \frac{\Delta R}{R} + \frac{\Delta t}{t} = 2(2\%) + 1\% + 1\% = 4\% + 1\% + 1\% = 6\%$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>$\pm 3.5\%$</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>উৎপন্ন তাপে শতকরা অনিশ্চয়তা $6\%$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6427,7 +6014,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 49</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6436,34 +6023,29 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: মাত্রীয় সমীকরণ দ্বারা অজানা ঘাত নির্ণয় 49]
-একটি ত্বরান্বিত তরল ফোঁটার কম্পাঙ্ক $n$ তরলের পৃষ্ঠটান $T$, ঘনত্ব $\rho$ এবং ব্যাসার্ধ $r$-এর ওপর নির্ভর করে: $n = k T^x \rho^y r^z$। মাত্রাগত সমীকরণ দ্বারা $x, y, z$-এর মান নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=1.5][size:small]##
+একটি তারের মধ্য দিয়ে প্রবাহিত তড়িৎ পরিমাপে অ্যামিটারের পাঠ $I = 2.50	ext{ A}$ কিন্তু এর সঠিক মান $2.42	ext{ A}$ হলে পরিমাপে পরম ত্রুটি ও আপেক্ষিক ত্রুটির শতকরা মান কত?</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>$[n] = [T^{-1}]$।
-$[T] = [MT^{-2}], [\rho] = [ML^{-3}], [r] = [L]$।
-$[M^0 L^0 T^{-1}] = [M^{x+y} L^{-3y+z} T^{-2x}]$।
-$-2x = -1 \implies x = 1/2$।
-$x + y = 0 \implies y = -1/2$।
-$-3(-1/2) + z = 0 \implies z = -3/2$।</t>
+          <t>পরম ত্রুটি $\Delta I = 2.50 - 2.42 = +0.08\text{ A}$। আপেক্ষিক শতকরা ত্রুটি $= \frac{0.08}{2.42} \times 100\% = 3.306\% \approx 3.31\%$।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>$x = 1/2, y = -1/2, z = -3/2$</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>পরম ত্রুটি $+0.08\text{ A}$, আপেক্ষিক ত্রুটি $3.31\%$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6483,44 +6065,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 50</t>
+          <t>ত্রুটির প্রকারভেদ ও ত্রুটির সঞ্চারণ (Error Propagation)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##
-[সমস্যা 50: ভার্নিয়ার পরিমাপ ও রৈখিক পাঠ 50]
-একটি বিশেষ ল্যাবরেটরি ভার্নিয়ার স্কেলের মূল স্কেলের ক্ষুদ্রতম ঘরের মান $0.5\text{ mm}$। মূল স্কেলের $49$ ঘর ভার্নিয়ারের $50$ ঘরের সমান। একটি পাতলা শিটের পাঠ নেওয়ার সময় মূল স্কেলের পাঠ $12.5\text{ mm}$ এবং ভার্নিয়ার সমপাতন 50 হলে শিটটির সঠিক বেধ কত?</t>
+          <t>##GEO:rect[w=2.5,h=1][size:small]##
+সার্থক অঙ্ক (Significant figures) নিয়ম মেনে সমাধান কর: $3.85 	imes 10^{-2}	ext{ g} + 0.042	ext{ g} - 1.256 	imes 10^{-3}	ext{ g}$ এর ফলাফল কত?</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>##GEO:vernier[size:small]##</t>
+          <t>##GEO:rect[w=2.5,h=1][size:small]##</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>$VC = \frac{0.5}{50} = 0.01\text{ mm}$।
-বেধ $= 12.5 + (50 \times 0.01) = 13.0\text{ mm}$।</t>
+          <t>$3.85 \times 10^{-2} = 0.0385\text{ g}$, $0.042\text{ g}$, $1.256 \times 10^{-3} = 0.001256\text{ g}$। যোগফল $= 0.0385 + 0.042 - 0.001256 = 0.079244\text{ g}$। দশমিকের পর সবচেয়ে কম ঘর ৩টি ($0.042$), অতএব ফলাফল $= 0.079\text{ g}$।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>$13.0\text{ mm}$</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>ফলাফল $= 0.079\text{ g}$</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
